--- a/ai-training-prompt-engineering/deliverables/Prompt_Template_Configurator.xlsx
+++ b/ai-training-prompt-engineering/deliverables/Prompt_Template_Configurator.xlsx
@@ -84,12 +84,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="1177">
   <si>
     <t xml:space="preserve">Prompt Template Configurator</t>
   </si>
   <si>
-    <t xml:space="preserve">v1.0 · August 2026 · owner Oscar Penny · generated from prompt-library/taxonomy/ (the source of truth — edit there, rebuild with src/build_configurator_xlsx.py)</t>
+    <t xml:space="preserve">v1.1 · August 2026 · owner Oscar Penny · generated from prompt-library/taxonomy/ (the source of truth — edit there, rebuild with src/build_configurator_xlsx.py)</t>
   </si>
   <si>
     <t xml:space="preserve">How to use</t>
@@ -2828,19 +2828,22 @@
     <t xml:space="preserve">Who is answering: identity, expertise posture, and checkable behavioral commitments.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick the professional posture. It sets vocabulary, caution level, and what gets foregrounded — not IQ.</t>
+    <t xml:space="preserve">Pick the professional posture. It sets vocabulary, caution level, and what gets foregrounded — not IQ.
+WHY IT MATTERS: Sets the register the answer is written in — vocabulary, caution level, what gets foregrounded. Expert personas measurably improve domain description tasks, but a 162-persona study found no accuracy gain on factual questions: identity buys voice and focus, not IQ. (Salewski et al. 2023; Zheng et al. 2024)</t>
   </si>
   <si>
     <t xml:space="preserve">Domain expertise</t>
   </si>
   <si>
-    <t xml:space="preserve">Name the field so the right vocabulary and priorities surface. This foregrounds knowledge — it does not create it.</t>
+    <t xml:space="preserve">Name the field so the right vocabulary and priorities surface. This foregrounds knowledge — it does not create it.
+WHY IT MATTERS: Naming the field surfaces its vocabulary, defaults, and priorities — the answer starts from the right corner of the model's training instead of the generic middle. It foregrounds knowledge the model already has; it cannot create knowledge it lacks. (Salewski et al. 2023; vendor role guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">Behavioral commitments · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The checkable rules — the part of Role that actually changes output. Pick from the three families below.</t>
+    <t xml:space="preserve">The checkable rules — the part of Role that actually changes output. Pick from the three families below.
+WHY IT MATTERS: The part of Role that measurably changes output: a behavioral rule is checkable line-by-line in the result, where a title is a vibe. Grounding-style rules are the documented lever for drastically reducing invented content. (Anthropic reduce-hallucinations guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">Behavioral commitments · choice 2</t>
@@ -2849,7 +2852,8 @@
     <t xml:space="preserve">    Accuracy behaviors · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">For anything with facts and numbers.</t>
+    <t xml:space="preserve">For anything with facts and numbers.
+WHY IT MATTERS: Training rewards a confident guess over an honest blank, so guessing is the default; accuracy rules re-open the abstain option. Compute-via-code exists because model arithmetic degrades sharply as numbers grow. (OpenAI 2025, why LMs hallucinate; Faith &amp; Fate, NeurIPS 2023)</t>
   </si>
   <si>
     <t xml:space="preserve">    Accuracy behaviors · choice 2</t>
@@ -2861,7 +2865,8 @@
     <t xml:space="preserve">    Transparency behaviors · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Make the work auditable.</t>
+    <t xml:space="preserve">Make the work auditable.
+WHY IT MATTERS: Stated assumptions and shown work convert an answer you must trust into one you can audit — errors surface at review, not downstream. Self-checking works only against concrete criteria like these; a bare 'are you sure?' can make answers worse. (Anthropic self-check guidance; Huang et al. 2024)</t>
   </si>
   <si>
     <t xml:space="preserve">    Transparency behaviors · choice 2</t>
@@ -2873,7 +2878,8 @@
     <t xml:space="preserve">    Style behaviors · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">How it writes, stated as rules.</t>
+    <t xml:space="preserve">How it writes, stated as rules.
+WHY IT MATTERS: Style stated as rules survives; style stated as adjectives drifts. 'One idea per sentence' is enforceable and checkable in the output — 'write clearly' is re-interpreted on every run. (vendor format guidance; prompt-sensitivity research)</t>
   </si>
   <si>
     <t xml:space="preserve">    Style behaviors · choice 2</t>
@@ -2882,7 +2888,8 @@
     <t xml:space="preserve">    Style behaviors · choice 3</t>
   </si>
   <si>
-    <t xml:space="preserve">The critical posture. Blind the model to your preference — it mirrors any side you reveal.</t>
+    <t xml:space="preserve">The critical posture. Blind the model to your preference — it mirrors any side you reveal.
+WHY IT MATTERS: Models affirm users ~49% more than humans do and mirror whichever side you reveal — a single flattering exchange measurably raises the user's conviction. Declaring a neutral or adversarial stance up front pre-empts the mirror before it engages. (Cheng et al., Science 2026; Sharma et al. 2023)</t>
   </si>
   <si>
     <t xml:space="preserve">Task  ★</t>
@@ -2891,55 +2898,65 @@
     <t xml:space="preserve">The single clear ask: verb + object + audience + success criterion.</t>
   </si>
   <si>
-    <t xml:space="preserve">Each verb is a mini-template — pick one and fill its {{slots}}, or write your own statement below.</t>
+    <t xml:space="preserve">Each verb is a mini-template — pick one and fill its {{slots}}, or write your own statement below.
+WHY IT MATTERS: The verb is the operation: it selects what transformation runs on your material and what 'done' looks like. Google's guidance calls the task verb 'the most important component of a prompt' — vague verbs produce exploration instead of answers. (Google Workspace prompting guide)</t>
   </si>
   <si>
     <t xml:space="preserve">Task statement</t>
   </si>
   <si>
-    <t xml:space="preserve">Or write the ask yourself — one task, one sentence if you can manage it.</t>
+    <t xml:space="preserve">Or write the ask yourself — one task, one sentence if you can manage it.
+WHY IT MATTERS: One task in one sentence is the highest-leverage clarity move: current reasoning models pay a real cost for ambiguity — they burn thinking tokens trying to reconcile vague or conflicting instructions instead of answering. (OpenAI GPT-5 guide; Anthropic 'be clear and direct')</t>
   </si>
   <si>
     <t xml:space="preserve">Example (replace): what is the return rate by site for Q2 vs the 2.0% target?</t>
   </si>
   <si>
-    <t xml:space="preserve">Who receives this and what they already know. It sets altitude and vocabulary.</t>
+    <t xml:space="preserve">Who receives this and what they already know. It sets altitude and vocabulary.
+WHY IT MATTERS: Audience re-ranks and re-words the same content: what leads, what gets cut, which terms need expansion. Without one, the model writes for nobody in particular — the mid-distribution reader who doesn't exist in your building. (vendor Persona/Context frameworks)</t>
   </si>
   <si>
     <t xml:space="preserve">    Reader's time budget</t>
   </si>
   <si>
-    <t xml:space="preserve">How long they'll actually give it — the honest constraint.</t>
+    <t xml:space="preserve">How long they'll actually give it — the honest constraint.
+WHY IT MATTERS: The honest constraint that forces compression: a 30-second reader gets the number and the ask; a 10-minute reader gets the reasoning. Left uncapped, models default to thorough — which the reader experiences as long. (practitioner consensus; length is a vendor API dial for this reason)</t>
   </si>
   <si>
     <t xml:space="preserve">    Reading level</t>
   </si>
   <si>
-    <t xml:space="preserve">The Canvas-style slider, as options. Plain-language guidance targets 6th–8th grade for general audiences.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The task's own completion test — what must be true of the output.</t>
+    <t xml:space="preserve">The Canvas-style slider, as options. Plain-language guidance targets 6th–8th grade for general audiences.
+WHY IT MATTERS: Vocabulary altitude is a dial the model follows reliably — and its default sits well above general-audience reading. Plain-language practice targets 6th–8th grade for mixed audiences; say the level and it lands there. (plain-language standards; style-prompting research)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The task's own completion test — what must be true of the output.
+WHY IT MATTERS: A stated completion test gives the model a target to optimize toward and gives you a check to run afterward — the same mechanism that makes self-verification work: concrete criteria catch errors reliably; vague quality asks don't. (Anthropic self-check guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">Purpose — why it matters</t>
   </si>
   <si>
-    <t xml:space="preserve">The decision or event this feeds. Models generalize from reasons — and it filters what matters.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Have the model confirm understanding before doing the work — cheapest error catch there is.</t>
+    <t xml:space="preserve">The decision or event this feeds. Models generalize from reasons — and it filters what matters.
+WHY IT MATTERS: Models generalize from reasons: 'no ellipses — this will be read aloud by text-to-speech' outperforms the bare rule, because the model extends the spirit to cases you didn't list. Purpose also filters relevance — it now knows what matters to the decision. (Anthropic explain-why guidance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Have the model confirm understanding before doing the work — cheapest error catch there is.
+WHY IT MATTERS: A restate-before-work step catches a misread task at the cheapest possible point — before any output exists. It is the generative version of the agentic Phase-0 intake gate: pennies to fix here, a full redo after a polished wrong answer. (plan-approval gate pattern)</t>
   </si>
   <si>
     <t xml:space="preserve">Everything true in your world that isn't in the training data — material, definitions, quirks, constraints, and the reasons behind rules.</t>
   </si>
   <si>
-    <t xml:space="preserve">The stuff to work from. Long documents go FIRST in the final prompt, instructions after — and delimit so material is never mistaken for instructions.</t>
+    <t xml:space="preserve">The stuff to work from. Long documents go FIRST in the final prompt, instructions after — and delimit so material is never mistaken for instructions.
+WHY IT MATTERS: Placement measurably matters: long documents at the TOP with the question at the END improved answers by up to ~30% in vendor testing, and accuracy sags for content buried in the middle of a long context. (Anthropic long-context guidance; Liu et al. 2023, lost in the middle)</t>
   </si>
   <si>
     <t xml:space="preserve">Glossary — controlled vocabulary · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Terms with local meaning. For metrics: numerator, denominator, grain, inclusions/exclusions — or the model will compute its own version.</t>
+    <t xml:space="preserve">Terms with local meaning. For metrics: numerator, denominator, grain, inclusions/exclusions — or the model will compute its own version.
+WHY IT MATTERS: The model resolves every undefined term to its most common global meaning — not your local one. A metric card (numerator, denominator, grain, exclusions) replaces the single biggest source of wrong analytical answers: a guessed denominator. (hallucination mechanics; data-analysis field practice)</t>
   </si>
   <si>
     <t xml:space="preserve">Glossary — controlled vocabulary · choice 2</t>
@@ -2948,7 +2965,8 @@
     <t xml:space="preserve">Known quirks → rules · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Every quirk you don't write down becomes a silent 'fix' the model invents. Pair each with its rule.</t>
+    <t xml:space="preserve">Every quirk you don't write down becomes a silent 'fix' the model invents. Pair each with its rule.
+WHY IT MATTERS: Every quirk you don't write down becomes a silent 'fix' the model invents — plausibility fills the gap, fluently. A quirk paired with its rule converts a hidden landmine into a followed instruction. (OpenAI 2025, why LMs hallucinate)</t>
   </si>
   <si>
     <t xml:space="preserve">Known quirks → rules · choice 2</t>
@@ -2960,7 +2978,8 @@
     <t xml:space="preserve">Constraints &amp; sensitivities · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">What must not happen — stated positively where possible, with the reason where it isn't obvious.</t>
+    <t xml:space="preserve">What must not happen — stated positively where possible, with the reason where it isn't obvious.
+WHY IT MATTERS: Positively-phrased constraints are followed more reliably than prohibitions — earlier models showed inverse scaling on negated instructions, and current vendor guidance remains 'tell it what TO do.' When you must forbid, attach the reason. (Anthropic guidance; Jang et al. 2022)</t>
   </si>
   <si>
     <t xml:space="preserve">Constraints &amp; sensitivities · choice 2</t>
@@ -2972,19 +2991,22 @@
     <t xml:space="preserve">The why behind the rules</t>
   </si>
   <si>
-    <t xml:space="preserve">Explain any non-obvious rule — "this will be read aloud, so no ellipses" outperforms "no ellipses." Models generalize from reasons.</t>
+    <t xml:space="preserve">Explain any non-obvious rule — "this will be read aloud, so no ellipses" outperforms "no ellipses." Models generalize from reasons.
+WHY IT MATTERS: The reason behind a rule is itself an instruction: models apply explained rules in spirit, not just letter, extending them to cases you didn't enumerate — the vendor docs state this generalization effect verbatim. (Anthropic best practices)</t>
   </si>
   <si>
     <t xml:space="preserve">The output contract: shape, length, tone, and what must be in or out.</t>
   </si>
   <si>
-    <t xml:space="preserve">The deliverable's shape. Name the columns for tables, the sections for documents.</t>
+    <t xml:space="preserve">The deliverable's shape. Name the columns for tables, the sections for documents.
+WHY IT MATTERS: Naming the deliverable's shape — a table with these columns, a memo with these sections — removes the largest degree of freedom the model would otherwise spend guessing, and makes output land ready to use instead of ready to reformat. (all four vendor frameworks: Format / Expectations)</t>
   </si>
   <si>
     <t xml:space="preserve">Structure rules · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The internal skeleton — where the answer sits, what every section carries.</t>
+    <t xml:space="preserve">The internal skeleton — where the answer sits, what every section carries.
+WHY IT MATTERS: Trivial format differences swing measured accuracy by up to 76 points across phrasings — structure is not cosmetic. A fixed, tested skeleton removes that variance and puts the answer where the reader looks first. (Sclar et al., ICLR 2024)</t>
   </si>
   <si>
     <t xml:space="preserve">Structure rules · choice 2</t>
@@ -2993,13 +3015,15 @@
     <t xml:space="preserve">Structure rules · choice 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Numeric, with a priority rule. Adjectives ("brief") are unenforceable; uncapped AI runs 2–3× long.</t>
+    <t xml:space="preserve">Numeric, with a priority rule. Adjectives ("brief") are unenforceable; uncapped AI runs 2–3× long.
+WHY IT MATTERS: A numeric cap is enforceable; 'brief' is a mood. Uncapped, models run two to three times longer than the reader needs — length is so real a dial that vendors expose it as an API parameter. The famous $200-tip stunt produced ~11% longer answers, not better ones. (OpenAI verbosity; tip-experiment analyses)</t>
   </si>
   <si>
     <t xml:space="preserve">Tone · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Compose from the three dials below — one pick per dial reads best.</t>
+    <t xml:space="preserve">Compose from the three dials below — one pick per dial reads best.
+WHY IT MATTERS: Tone is where role prompting genuinely pays: models imitate a specified register reliably, and register changes how the human reader receives the work. Compose it from dials rather than adjectives — one pick per dial reads best. (vendor role-for-tone position; style-prompting research)</t>
   </si>
   <si>
     <t xml:space="preserve">Tone · choice 2</t>
@@ -3008,19 +3032,30 @@
     <t xml:space="preserve">    Formality</t>
   </si>
   <si>
+    <t xml:space="preserve">WHY IT MATTERS: Formality sets the social distance of the prose — hallway versus boardroom. Models default to mid-formal; one explicit pick lands it where you need it. (style-prompting research)</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Directness</t>
   </si>
   <si>
+    <t xml:space="preserve">WHY IT MATTERS: Directness decides whether the ask or the courtesy leads. Models hedge by default — caution is trained in — so 'lead with the ask' has to be said to happen. (practitioner consensus; headline-first practice)</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Warmth</t>
   </si>
   <si>
-    <t xml:space="preserve">Vocabulary altitude and jargon policy.</t>
+    <t xml:space="preserve">WHY IT MATTERS: Warmth calibrates the relationship signals in the text. Unmanaged, it drifts toward affirmation — the same preference-training pressure behind sycophancy — so the dial keeps warmth a choice rather than a bias. (Sharma et al. 2023, sycophancy origins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vocabulary altitude and jargon policy.
+WHY IT MATTERS: Jargon policy decides who can act on the output without a translator. Models also mirror the prompt's own vocabulary — write at the altitude you want back. (Anthropic: match your prompt's style to the desired output)</t>
   </si>
   <si>
     <t xml:space="preserve">Must include / must not · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The inclusion contract.</t>
+    <t xml:space="preserve">The inclusion contract.
+WHY IT MATTERS: An explicit include/exclude list turns review into a checklist — presence and absence verified in seconds instead of re-reading for feel. It is the format-level version of checkable behavioral rules. (self-check-against-criteria guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">Must include / must not · choice 2</t>
@@ -3029,31 +3064,36 @@
     <t xml:space="preserve">Must include / must not · choice 3</t>
   </si>
   <si>
-    <t xml:space="preserve">Ask for alternatives to choose from — divergence as a dial. You become the selector, not the author.</t>
+    <t xml:space="preserve">Ask for alternatives to choose from — divergence as a dial. You become the selector, not the author.
+WHY IT MATTERS: Asking for N alternatives converts sampling variance from a bug into a menu — the insight behind self-consistency, where several sampled answers beat any single one. You become the selector, which is where your judgment belongs. (Wang et al. 2023, self-consistency)</t>
   </si>
   <si>
     <t xml:space="preserve">3–5 realistic demonstrations of the task done right — the strongest steering signal there is.</t>
   </si>
   <si>
-    <t xml:space="preserve">Zero-shot first on thinking models; add examples when format drifts. More helps most on formatting/labeling tasks.</t>
+    <t xml:space="preserve">Zero-shot first on thinking models; add examples when format drifts. More helps most on formatting/labeling tasks.
+WHY IT MATTERS: Few-shot examples were the original prompt-engineering discovery: task performance from demonstrations alone, no retraining. 3–5 diverse examples steer format and tone most reliably — but start zero-shot on thinking models; few-shot measurably degrades some of them. (Brown et al. 2020; Anthropic guidance; DeepSeek-R1 paper)</t>
   </si>
   <si>
     <t xml:space="preserve">Coverage · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Which cases your examples span — the model's boundary behavior copies theirs.</t>
+    <t xml:space="preserve">Which cases your examples span — the model's boundary behavior copies theirs.
+WHY IT MATTERS: The model copies your examples' boundary behavior, not just their shape: exemplar choice and order alone can swing accuracy from near-chance to over 90%. All-happy-path examples teach it to treat every case as happy — one typical + one edge + one reject teaches the standard. (Lu et al. 2021; Prompt Report design decisions)</t>
   </si>
   <si>
     <t xml:space="preserve">Coverage · choice 2</t>
   </si>
   <si>
-    <t xml:space="preserve">Fence examples so they can't be mistaken for live input.</t>
+    <t xml:space="preserve">Fence examples so they can't be mistaken for live input.
+WHY IT MATTERS: Fencing examples in tags keeps them from being read as live input or instructions — unambiguous parsing is the documented reason vendors recommend tag structure, and unfenced examples are the classic source of example text leaking into output. (Anthropic XML-tags guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">The examples</t>
   </si>
   <si>
-    <t xml:space="preserve">Paste them. Real (redacted) beats invented; lightly-genericized real beats both.</t>
+    <t xml:space="preserve">Paste them. Real (redacted) beats invented; lightly-genericized real beats both.
+WHY IT MATTERS: Models imitate surface detail as much as structure — a real (redacted) example carries your house style's actual distribution; an invented one carries what the model guesses your style is. Exemplar quality and similarity are measured few-shot design decisions. (Prompt Report §2.2)</t>
   </si>
   <si>
     <t xml:space="preserve">Permission to not know — re-opens the abstain option that benchmark training closed.</t>
@@ -3062,7 +3102,8 @@
     <t xml:space="preserve">When it applies · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The situations where not-knowing must surface instead of being papered over.</t>
+    <t xml:space="preserve">The situations where not-knowing must surface instead of being papered over.
+WHY IT MATTERS: Standard training rewards a confident guess over 'I don't know' — benchmarks score the guess, so guessing is the default. Naming the exact situations where not-knowing must surface re-opens the abstain option precisely where it matters. (OpenAI 2025, why LMs hallucinate)</t>
   </si>
   <si>
     <t xml:space="preserve">When it applies · choice 2</t>
@@ -3071,7 +3112,8 @@
     <t xml:space="preserve">When it applies · choice 3</t>
   </si>
   <si>
-    <t xml:space="preserve">The escape hatch's shape.</t>
+    <t xml:space="preserve">The escape hatch's shape.
+WHY IT MATTERS: Explicitly permitting 'I don't know' 'can drastically reduce false information' — the vendor's own wording. Giving the escape hatch a shape (say so, ask, or flag and continue) converts invisible guesses into visible, handleable items. (Anthropic reduce-hallucinations, verbatim)</t>
   </si>
   <si>
     <t xml:space="preserve">The scope boundary — converts open-ended capability into bounded work.</t>
@@ -3080,28 +3122,33 @@
     <t xml:space="preserve">Scope</t>
   </si>
   <si>
-    <t xml:space="preserve">Numbered, in priority order — the model works down the list.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Where work ends — or pauses for you.</t>
+    <t xml:space="preserve">Numbered, in priority order — the model works down the list.
+WHY IT MATTERS: A numbered scope list is an execution order: the model works down it instead of wandering sideways. Explicit scope and stop criteria are how vendors now control model 'eagerness' — the same dial, applied to text work. (OpenAI GPT-5 guidance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where work ends — or pauses for you.
+WHY IT MATTERS: An explicit end condition prevents both default failures: stopping early with a partial answer, and padding on past the answer. For anything loop-like, stopping conditions are a control requirement, not a nicety. (Anthropic building-effective-agents)</t>
   </si>
   <si>
     <t xml:space="preserve">Explicitly out of scope</t>
   </si>
   <si>
-    <t xml:space="preserve">Name the adjacent things NOT to touch.</t>
+    <t xml:space="preserve">Name the adjacent things NOT to touch.
+WHY IT MATTERS: Models err toward helpful overreach — adjacent questions get answered because they can be. Naming the not-asked keeps output on the question you actually have: the manual version of a relevance guardrail. (OpenAI guardrail categories)</t>
   </si>
   <si>
     <t xml:space="preserve">The standing behavioral contract — biases hundreds of unsupervised decisions, not one answer.</t>
   </si>
   <si>
-    <t xml:space="preserve">The job-shaped identity. Compound postures (engineer + analyst + writer) prevent single-lens blind spots.</t>
+    <t xml:space="preserve">The job-shaped identity. Compound postures (engineer + analyst + writer) prevent single-lens blind spots.
+WHY IT MATTERS: An agent's posture persists across hundreds of unsupervised decisions, so it must be job-shaped, not title-shaped. Compound postures (engineer + analyst + writer) prevent the single-lens failure where every problem gets one discipline's answer. (agent-design practice; Anthropic agent guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">Standing behaviors · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The rules that must survive hour three of a long run.</t>
+    <t xml:space="preserve">The rules that must survive hour three of a long run.
+WHY IT MATTERS: Long runs outlive their own context — what was said in minute one has faded by hour three. Standing behaviors are the conduct that must hold when nothing recent reinforces it, which is why harness guidance bakes rules into re-read files rather than conversation. (Anthropic long-running-agents harness)</t>
   </si>
   <si>
     <t xml:space="preserve">Standing behaviors · choice 2</t>
@@ -3122,34 +3169,40 @@
     <t xml:space="preserve">Goal</t>
   </si>
   <si>
-    <t xml:space="preserve">One sentence: the question to answer or the thing to produce.</t>
+    <t xml:space="preserve">One sentence: the question to answer or the thing to produce.
+WHY IT MATTERS: One goal sentence is the loop's objective function: gather → act → verify → repeat runs 'until the goal is met.' Two goals in one brief make every prioritization a coin-flip you never see. (Anthropic agent-loop framing)</t>
   </si>
   <si>
     <t xml:space="preserve">Decision it supports</t>
   </si>
   <si>
-    <t xml:space="preserve">What someone will do differently depending on the answer — filters everything downstream.</t>
+    <t xml:space="preserve">What someone will do differently depending on the answer — filters everything downstream.
+WHY IT MATTERS: Naming the decision the work supports filters everything downstream — which findings matter, what precision suffices, what is noise. It is the brief-level relevance guardrail: scope drift dies here. (OpenAI relevance-guardrail concept; mission-brief practice)</t>
   </si>
   <si>
     <t xml:space="preserve">Audience &amp; deadline</t>
   </si>
   <si>
-    <t xml:space="preserve">Who sees it, how long they'll give it, and when it's due.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">One-off or recurring changes the economics: recurring jobs get standing briefs.</t>
+    <t xml:space="preserve">Who sees it, how long they'll give it, and when it's due.
+WHY IT MATTERS: Audience and deadline set the depth-versus-speed tradeoffs the agent will otherwise make for you, silently. A 30-second executive read and a hard due date change method choices all the way down the pipeline. (practitioner consensus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One-off or recurring changes the economics: recurring jobs get standing briefs.
+WHY IT MATTERS: One-off versus recurring changes the economics of the whole brief: recurring jobs justify standing briefs, delta reporting, and versioned definitions — where agentic prompting pays compound interest. (reuse-by-diff pattern; AGENTS.md practice)</t>
   </si>
   <si>
     <t xml:space="preserve">Done looks like</t>
   </si>
   <si>
-    <t xml:space="preserve">The deliverables in one line — exact and countable.</t>
+    <t xml:space="preserve">The deliverables in one line — exact and countable.
+WHY IT MATTERS: The loop needs an exit condition it can evaluate. 'Done looks like: three files, named thus' is countable; without it agents stop early or run forever — the documented failure that structured task lists with pass flags exist to prevent. (Anthropic harness: feature-list pattern)</t>
   </si>
   <si>
     <t xml:space="preserve">Verifiable by · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The check the agent can actually run to know it's done — the single highest-leverage line in an agentic prompt.</t>
+    <t xml:space="preserve">The check the agent can actually run to know it's done — the single highest-leverage line in an agentic prompt.
+WHY IT MATTERS: The single highest-leverage line in a brief. The vendor's own rule for long-running agents: mark work complete 'only after end-to-end verification confirms it works, not when the code is written.' A done-check the agent can run converts 'I finished' into 'it passed.' (Anthropic memory-tool guidance, verbatim)</t>
   </si>
   <si>
     <t xml:space="preserve">Verifiable by · choice 2</t>
@@ -3164,13 +3217,15 @@
     <t xml:space="preserve">Domain in three sentences</t>
   </si>
   <si>
-    <t xml:space="preserve">The process, the actors, what 'good' means.</t>
+    <t xml:space="preserve">The process, the actors, what 'good' means.
+WHY IT MATTERS: Three sentences of process, actors, and what 'good' means give every downstream judgment a frame. Without them the agent optimizes for generic best practice — generically right, specifically wrong for your operation. (context-element mechanics)</t>
   </si>
   <si>
     <t xml:space="preserve">Glossary (controlled vocabulary) · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Every metric as a card: numerator, denominator, grain, inclusions, exclusions. The agent will otherwise compute three subtly different versions.</t>
+    <t xml:space="preserve">Every metric as a card: numerator, denominator, grain, inclusions, exclusions. The agent will otherwise compute three subtly different versions.
+WHY IT MATTERS: An agent touches every source repeatedly: a guessed denominator doesn't make one wrong sentence — it propagates through every transformation, chart, and slide of the run. Metric cards make definitions load-bearing once and correct everywhere. (source-register discipline; pipeline field practice)</t>
   </si>
   <si>
     <t xml:space="preserve">Glossary (controlled vocabulary) · choice 2</t>
@@ -3179,16 +3234,19 @@
     <t xml:space="preserve">Entities &amp; identifiers</t>
   </si>
   <si>
-    <t xml:space="preserve">Part numbers, site names, aliases, vendor codes — spelled the way the audience spells them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Things that have bitten before, each with the rule that disarms it.</t>
+    <t xml:space="preserve">Part numbers, site names, aliases, vendor codes — spelled the way the audience spells them.
+WHY IT MATTERS: Exact identifiers, spelled the way the audience spells them, prevent silent fuzzy matching — the join on 'almost the same part number' that poisons a dataset without raising an error. Enumerated entities turn matching into lookup. (data-pipeline practice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Things that have bitten before, each with the rule that disarms it.
+WHY IT MATTERS: Each known quirk with its disarming rule converts institutional scar tissue into instructions. Undocumented, the same quirk gets 'fixed' differently every run — plausibly, silently, and sometimes destructively. (hallucination mechanics applied to data)</t>
   </si>
   <si>
     <t xml:space="preserve">Targets &amp; prior work</t>
   </si>
   <si>
-    <t xml:space="preserve">Thresholds that matter, and files or decisions the output must stay consistent with.</t>
+    <t xml:space="preserve">Thresholds that matter, and files or decisions the output must stay consistent with.
+WHY IT MATTERS: Thresholds and previously-published numbers are the run's consistency constraints: they anchor new output to figures the organization already trusts and make drift a detectable event instead of a surprise in a meeting. (reconciliation-anchor family)</t>
   </si>
   <si>
     <t xml:space="preserve">Environment  ★</t>
@@ -3200,13 +3258,15 @@
     <t xml:space="preserve">Workspace</t>
   </si>
   <si>
-    <t xml:space="preserve">Repo/folder and branch. One initiative, one folder.</t>
+    <t xml:space="preserve">Repo/folder and branch. One initiative, one folder.
+WHY IT MATTERS: One initiative, one folder is blast-radius design: everything the run touches is enumerable, backupable, revertable. It also makes sessions reproducible — harness practice starts every session by re-reading the same workspace. (Anthropic harness: per-session ritual)</t>
   </si>
   <si>
     <t xml:space="preserve">Read/write boundaries · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The three-zone layout: immutable inputs, versioned outputs, regenerable scratch.</t>
+    <t xml:space="preserve">The three-zone layout: immutable inputs, versioned outputs, regenerable scratch.
+WHY IT MATTERS: The three-zone layout engineers reversibility in before any action runs: immutable inputs can't be corrupted, versioned outputs can't be silently overwritten, scratch is disposable by contract. Vendor tooling enforces the same idea as protected paths and blocked destructive commands. (Claude Code permission modes; git-revert harness practice)</t>
   </si>
   <si>
     <t xml:space="preserve">Read/write boundaries · choice 2</t>
@@ -3215,7 +3275,8 @@
     <t xml:space="preserve">Tools allowed · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Name what exists. Anything unnamed is a guess.</t>
+    <t xml:space="preserve">Name what exists. Anything unnamed is a guess.
+WHY IT MATTERS: Least privilege starts with naming what exists — anything unnamed is a guess the agent may make for you. Published guidance risk-rates every tool (low/medium/high) by write access, reversibility, and impact; the allowed list is where that rating lives. (OpenAI practical guide, tool safeguards)</t>
   </si>
   <si>
     <t xml:space="preserve">Tools allowed · choice 2</t>
@@ -3227,7 +3288,8 @@
     <t xml:space="preserve">Forbidden actions · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The explicit denylist — name what would be assumed available otherwise.</t>
+    <t xml:space="preserve">The explicit denylist — name what would be assumed available otherwise.
+WHY IT MATTERS: An explicit denylist beats an implied one because evaluation order is deny-first: what is forbidden stays forbidden regardless of what else allows it. Name what would otherwise be assumed available — email, deletion, posting. (permission-rule precedence: deny &gt; ask &gt; allow)</t>
   </si>
   <si>
     <t xml:space="preserve">Forbidden actions · choice 2</t>
@@ -3239,7 +3301,8 @@
     <t xml:space="preserve">Confidentiality · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">What may leave the workspace, and in what form.</t>
+    <t xml:space="preserve">What may leave the workspace, and in what form.
+WHY IT MATTERS: The documented exfiltration pattern needs three legs at once: private data, untrusted content, and an outbound channel. The confidentiality clause removes or narrows the outbound leg — say what may leave the workspace, and in what form. (lethal-trifecta analysis; PII-filter guardrails)</t>
   </si>
   <si>
     <t xml:space="preserve">Confidentiality · choice 2</t>
@@ -3248,7 +3311,8 @@
     <t xml:space="preserve">Action risk policy · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">How actions are triaged by consequence — the published patterns.</t>
+    <t xml:space="preserve">How actions are triaged by consequence — the published patterns.
+WHY IT MATTERS: Triaging actions by consequence is the published pattern on both major stacks: reversible proceeds, irreversible asks — operationalized as low/medium/high tool ratings and never/maybe/always-irreversible action classes. (OpenAI practical guide; Magentic-UI action guards)</t>
   </si>
   <si>
     <t xml:space="preserve">Action risk policy · choice 2</t>
@@ -3260,19 +3324,22 @@
     <t xml:space="preserve">Source register</t>
   </si>
   <si>
-    <t xml:space="preserve">One block per source. The skeleton below is the discipline — fill every line or write UNKNOWN.</t>
+    <t xml:space="preserve">One block per source. The skeleton below is the discipline — fill every line or write UNKNOWN.
+WHY IT MATTERS: A source register makes every input's location, format, grain, and meaning explicit before anything is computed — profiling before processing. Skipped, the first wrong assumption about what one row means propagates through the entire run. (ETL discipline)</t>
   </si>
   <si>
     <t xml:space="preserve">Trust levels · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Declare per source — trust level dictates validation depth.</t>
+    <t xml:space="preserve">Declare per source — trust level dictates validation depth.
+WHY IT MATTERS: Trust level dictates validation depth — the data-side version of tool risk ratings: a system export and a hand-typed tracker must not get the same scrutiny. Declaring it routes checking effort to where errors actually live. (risk-rating pattern applied to sources)</t>
   </si>
   <si>
     <t xml:space="preserve">Trust levels · choice 2</t>
   </si>
   <si>
-    <t xml:space="preserve">The register's cardinal rule.</t>
+    <t xml:space="preserve">The register's cardinal rule.
+WHY IT MATTERS: 'Write UNKNOWN, never guess' turns the model's strongest failure mode — plausible gap-filling — into a logged, owned item. An UNKNOWN is a work item; a guess is a landmine with a delay. (abstention research applied to pipelines)</t>
   </si>
   <si>
     <t xml:space="preserve">Bounded method: the steps in order, methods allowed, methods requiring permission.</t>
@@ -3281,13 +3348,15 @@
     <t xml:space="preserve">Steps</t>
   </si>
   <si>
-    <t xml:space="preserve">Each step: what it consumes, what it produces.</t>
+    <t xml:space="preserve">Each step: what it consumes, what it produces.
+WHY IT MATTERS: Steps with named inputs and outputs make intermediates inspectable — the documented reason explicit pipelines still matter: 'useful when you need to inspect intermediate outputs or enforce a specific pipeline structure.' Audit trails are built here. (Anthropic chaining guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">Methods allowed · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Boring and reproducible. The default analytical toolkit.</t>
+    <t xml:space="preserve">Boring and reproducible. The default analytical toolkit.
+WHY IT MATTERS: Boring, reproducible methods are a feature: descriptive stats and run charts re-run identically and survive challenge; clever one-offs don't. Compute-via-code is non-negotiable — model arithmetic degrades sharply as the numbers grow. (Faith &amp; Fate, NeurIPS 2023)</t>
   </si>
   <si>
     <t xml:space="preserve">Methods allowed · choice 2</t>
@@ -3299,7 +3368,8 @@
     <t xml:space="preserve">Not without asking · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Propose at a gate; never just use.</t>
+    <t xml:space="preserve">Propose at a gate; never just use.
+WHY IT MATTERS: 'Propose at a gate, never just use' routes method escalation through a human — the high-risk and failure-threshold triggers vendors place on agent actions, applied to analysis choices that would change what the numbers mean. (OpenAI escalation guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">Not without asking · choice 2</t>
@@ -3317,13 +3387,15 @@
     <t xml:space="preserve">Reconciliation anchor</t>
   </si>
   <si>
-    <t xml:space="preserve">One number from OUTSIDE the run that the results must tie to. The most important single check.</t>
+    <t xml:space="preserve">One number from OUTSIDE the run that the results must tie to. The most important single check.
+WHY IT MATTERS: One number from outside the run that the results must tie to catches whole-pipeline errors — wrong filters, dropped rows, doubled joins — with a single comparison. Recalculate, scan for errors, tie out: the pattern vendor tooling mandates before delivery. (reconciliation/recalc practice)</t>
   </si>
   <si>
     <t xml:space="preserve">HARD checks (stop the run) · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Failure means stop, show the offending rows, and wait.</t>
+    <t xml:space="preserve">Failure means stop, show the offending rows, and wait.
+WHY IT MATTERS: Rules-based feedback is 'the best form of feedback' an agent gets — clear rules, plus which rule failed and why. HARD checks make the run fail loudly at the failure point instead of finishing wrong politely; showing the offending rows makes the failure debuggable. (Anthropic Agent SDK verify-work)</t>
   </si>
   <si>
     <t xml:space="preserve">HARD checks (stop the run) · choice 2</t>
@@ -3338,7 +3410,8 @@
     <t xml:space="preserve">SOFT checks (flag and continue) · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Suspicion, not failure — logged to open items.</t>
+    <t xml:space="preserve">Suspicion, not failure — logged to open items.
+WHY IT MATTERS: SOFT separates suspicion from failure so the run neither ignores anomalies nor cries wolf: flagged items land in open items with evidence attached, and a human triages them at review instead of mid-run. (check-type taxonomy; open-items discipline)</t>
   </si>
   <si>
     <t xml:space="preserve">SOFT checks (flag and continue) · choice 2</t>
@@ -3353,13 +3426,15 @@
     <t xml:space="preserve">Deliverables</t>
   </si>
   <si>
-    <t xml:space="preserve">Numbered, with the _MMDDYY convention and what each contains.</t>
+    <t xml:space="preserve">Numbered, with the _MMDDYY convention and what each contains.
+WHY IT MATTERS: Numbered deliverables with exact names make 'done' countable — the reason harness guidance tracks work as a structured list with pass flags rather than prose: it prevents premature completion and orphaned extras alike. (Anthropic harness: feature-list pattern)</t>
   </si>
   <si>
     <t xml:space="preserve">Logs · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The three files that make a run auditable.</t>
+    <t xml:space="preserve">The three files that make a run auditable.
+WHY IT MATTERS: CHANGES, FINDINGS, and OPEN_ITEMS make a run auditable after the fact — the 'structured updates' long-running-agent guidance requires every session to leave. Without logs there is no way to distinguish what the agent did from what it says it did. (Anthropic harness guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">Logs · choice 2</t>
@@ -3368,7 +3443,8 @@
     <t xml:space="preserve">Reproducibility · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The regeneration guarantee.</t>
+    <t xml:space="preserve">The regeneration guarantee.
+WHY IT MATTERS: The regeneration guarantee — same inputs, same command, same outputs — turns a deliverable into evidence. It is why outputs carry formulas rather than pasted values and why environments get an init script: reproducibility is engineered, not hoped for. (harness init-script pattern; workbook discipline)</t>
   </si>
   <si>
     <t xml:space="preserve">Reproducibility · choice 2</t>
@@ -3383,13 +3459,15 @@
     <t xml:space="preserve">Phases</t>
   </si>
   <si>
-    <t xml:space="preserve">Phase 0 is always intake: the agent restates the mission and its assumptions in its own words.</t>
+    <t xml:space="preserve">Phase 0 is always intake: the agent restates the mission and its assumptions in its own words.
+WHY IT MATTERS: Phase 0 — the agent restates the mission and its assumptions in its own words — is the cheapest error catch in the run: a misread brief costs pennies here and a full rerun later. Plan-then-approve is the documented pattern across vendor tooling. (Claude Code plan mode; Magentic-UI co-planning)</t>
   </si>
   <si>
     <t xml:space="preserve">Gates · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Human checkpoints, in ascending cost of the error they catch.</t>
+    <t xml:space="preserve">Human checkpoints, in ascending cost of the error they catch.
+WHY IT MATTERS: Gates put human judgment where published guidance puts it: before edits (plan approval), before irreversible or high-stakes actions, at failure thresholds, and at final review — each gate catching its error class at its cheapest point. (OpenAI practical guide; gate-placement survey)</t>
   </si>
   <si>
     <t xml:space="preserve">Gates · choice 2</t>
@@ -3401,7 +3479,8 @@
     <t xml:space="preserve">Autonomy rules · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Both halves matter: without 'proceed' you built a slow chatbot; without 'stop' you built a liability.</t>
+    <t xml:space="preserve">Both halves matter: without 'proceed' you built a slow chatbot; without 'stop' you built a liability.
+WHY IT MATTERS: Both halves are load-bearing: without proceed rules you built a slow chatbot that asks about everything; without stop rules you built a liability that asks about nothing. The published stop triggers are high-risk actions and exceeded failure thresholds. (OpenAI human-intervention guidance)</t>
   </si>
   <si>
     <t xml:space="preserve">Autonomy rules · choice 2</t>
@@ -3413,7 +3492,8 @@
     <t xml:space="preserve">Autonomy rules · choice 4</t>
   </si>
   <si>
-    <t xml:space="preserve">A deliberate design choice, separate from capability. Named by the role you keep — pick the lowest level that still gets the job done.</t>
+    <t xml:space="preserve">A deliberate design choice, separate from capability. Named by the role you keep — pick the lowest level that still gets the job done.
+WHY IT MATTERS: Autonomy is 'a deliberate design decision, separate from capability' — the published levels are named by the role the human keeps: operator, collaborator, consultant, approver, observer. Pick the lowest level that gets the job done; capability never obliges autonomy. (Feng et al. 2025)</t>
   </si>
   <si>
     <t xml:space="preserve">The non-negotiables — short, absolute, few — that must survive a long context.</t>
@@ -3422,7 +3502,8 @@
     <t xml:space="preserve">Invariants · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The standard set — prune to what this job actually needs.</t>
+    <t xml:space="preserve">The standard set — prune to what this job actually needs.
+WHY IT MATTERS: Invariants are the deterministic guardrail class — rules enforced as rules, not judgment calls: never invent data, never overwrite inputs, version everything. Deterministic protections are their own category in vendor guardrail taxonomies precisely because they don't degrade under pressure. (OpenAI rules-based protections)</t>
   </si>
   <si>
     <t xml:space="preserve">Invariants · choice 2</t>
@@ -3440,7 +3521,8 @@
     <t xml:space="preserve">Definition of done · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Tick-able, evidence-able items.</t>
+    <t xml:space="preserve">Tick-able, evidence-able items.
+WHY IT MATTERS: A definition of done as tick-able, evidence-able items is the anti-premature-completion device: 'passes' flips only on verification, and the checks themselves are out of bounds to edit — 'it is unacceptable to remove or edit tests.' (Anthropic harness, verbatim)</t>
   </si>
   <si>
     <t xml:space="preserve">Definition of done · choice 2</t>
@@ -3455,7 +3537,8 @@
     <t xml:space="preserve">Report shape · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The standard six lines — deselect only what genuinely doesn't apply.</t>
+    <t xml:space="preserve">The standard six lines — deselect only what genuinely doesn't apply.
+WHY IT MATTERS: A fixed report shape is why status reads in 30 seconds: the same lines in the same order every run, skimmable by humans and parseable by tools. Every agent SDK ships fixed result-status enums for the same reason — variable-shape reports hide failures. (SDK result/status enums)</t>
   </si>
   <si>
     <t xml:space="preserve">Report shape · choice 2</t>
@@ -3470,7 +3553,8 @@
     <t xml:space="preserve">Report discipline · choice 1</t>
   </si>
   <si>
-    <t xml:space="preserve">The rules that keep reports readable and honest.</t>
+    <t xml:space="preserve">The rules that keep reports readable and honest.
+WHY IT MATTERS: Evidence over assertion: 'done' means the check it ran, the output it got, and the file re-opened and verified — not the claim. Reports that cite their evidence convert trust from personality to track record, which is what agent oversight is supposed to run on. (harness verification guidance; NCSC oversight principle)</t>
   </si>
   <si>
     <t xml:space="preserve">Report discipline · choice 2</t>
@@ -10901,7 +10985,7 @@
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
     </row>
-    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
         <v>23</v>
@@ -10918,7 +11002,7 @@
         <v>You are a careful analyst.</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
         <v>915</v>
@@ -10933,7 +11017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
         <v>917</v>
@@ -10961,7 +11045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
         <v>920</v>
@@ -11004,7 +11088,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
       <c r="B10" s="10" t="s">
         <v>924</v>
@@ -11045,7 +11129,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
         <v>928</v>
@@ -11086,7 +11170,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9"/>
       <c r="B16" s="10" t="s">
         <v>128</v>
@@ -11113,7 +11197,7 @@
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9"/>
       <c r="B18" s="10" t="s">
         <v>145</v>
@@ -11130,7 +11214,7 @@
         <v>Answer: {{the question, with metric and period — e.g., "what is X by group for Q2 vs the target"}}?</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9"/>
       <c r="B19" s="10" t="s">
         <v>936</v>
@@ -11147,7 +11231,7 @@
         <v>Example (replace): what is the return rate by site for Q2 vs the 2.0% target?</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
         <v>194</v>
@@ -11162,7 +11246,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9"/>
       <c r="B21" s="10" t="s">
         <v>940</v>
@@ -11177,7 +11261,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9"/>
       <c r="B22" s="10" t="s">
         <v>942</v>
@@ -11192,7 +11276,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9"/>
       <c r="B23" s="10" t="s">
         <v>239</v>
@@ -11207,7 +11291,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9"/>
       <c r="B24" s="10" t="s">
         <v>945</v>
@@ -11222,7 +11306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9"/>
       <c r="B25" s="10" t="s">
         <v>252</v>
@@ -11249,7 +11333,7 @@
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
     </row>
-    <row r="27" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9"/>
       <c r="B27" s="10" t="s">
         <v>263</v>
@@ -11264,7 +11348,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9"/>
       <c r="B28" s="10" t="s">
         <v>950</v>
@@ -11292,7 +11376,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9"/>
       <c r="B30" s="10" t="s">
         <v>953</v>
@@ -11333,7 +11417,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9"/>
       <c r="B33" s="10" t="s">
         <v>957</v>
@@ -11374,7 +11458,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9"/>
       <c r="B36" s="10" t="s">
         <v>961</v>
@@ -11401,7 +11485,7 @@
       <c r="E37" s="8"/>
       <c r="F37" s="8"/>
     </row>
-    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9"/>
       <c r="B38" s="10" t="s">
         <v>316</v>
@@ -11416,7 +11500,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9"/>
       <c r="B39" s="10" t="s">
         <v>965</v>
@@ -11457,7 +11541,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9"/>
       <c r="B42" s="10" t="s">
         <v>381</v>
@@ -11472,7 +11556,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9"/>
       <c r="B43" s="10" t="s">
         <v>970</v>
@@ -11500,12 +11584,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9"/>
       <c r="B45" s="10" t="s">
         <v>973</v>
       </c>
-      <c r="C45" s="11"/>
+      <c r="C45" s="11" t="s">
+        <v>974</v>
+      </c>
       <c r="D45" s="15"/>
       <c r="E45" s="13"/>
       <c r="F45" s="14" t="str">
@@ -11513,12 +11599,14 @@
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9"/>
       <c r="B46" s="10" t="s">
-        <v>974</v>
-      </c>
-      <c r="C46" s="11"/>
+        <v>975</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>976</v>
+      </c>
       <c r="D46" s="15"/>
       <c r="E46" s="13"/>
       <c r="F46" s="14" t="str">
@@ -11526,12 +11614,14 @@
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9"/>
       <c r="B47" s="10" t="s">
-        <v>975</v>
-      </c>
-      <c r="C47" s="11"/>
+        <v>977</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>978</v>
+      </c>
       <c r="D47" s="15"/>
       <c r="E47" s="13"/>
       <c r="F47" s="14" t="str">
@@ -11539,13 +11629,13 @@
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9"/>
       <c r="B48" s="10" t="s">
         <v>463</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="D48" s="15"/>
       <c r="E48" s="13"/>
@@ -11554,13 +11644,13 @@
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9"/>
       <c r="B49" s="10" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="13"/>
@@ -11572,7 +11662,7 @@
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9"/>
       <c r="B50" s="10" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="15"/>
@@ -11585,7 +11675,7 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9"/>
       <c r="B51" s="10" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="15"/>
@@ -11595,13 +11685,13 @@
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9"/>
       <c r="B52" s="10" t="s">
         <v>494</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="13"/>
@@ -11615,20 +11705,20 @@
         <v>506</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
       <c r="F53" s="8"/>
     </row>
-    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9"/>
       <c r="B54" s="10" t="s">
         <v>507</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="13"/>
@@ -11637,13 +11727,13 @@
         <v/>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9"/>
       <c r="B55" s="10" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D55" s="15"/>
       <c r="E55" s="13"/>
@@ -11655,7 +11745,7 @@
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9"/>
       <c r="B56" s="10" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="15"/>
@@ -11665,13 +11755,13 @@
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9"/>
       <c r="B57" s="10" t="s">
         <v>527</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>987</v>
+        <v>990</v>
       </c>
       <c r="D57" s="15"/>
       <c r="E57" s="13"/>
@@ -11680,13 +11770,13 @@
         <v/>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9"/>
       <c r="B58" s="10" t="s">
-        <v>988</v>
+        <v>991</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>989</v>
+        <v>992</v>
       </c>
       <c r="D58" s="15"/>
       <c r="E58" s="13"/>
@@ -11700,20 +11790,20 @@
         <v>533</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
       <c r="F59" s="8"/>
     </row>
-    <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9"/>
       <c r="B60" s="10" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="D60" s="15"/>
       <c r="E60" s="13"/>
@@ -11725,7 +11815,7 @@
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9"/>
       <c r="B61" s="10" t="s">
-        <v>993</v>
+        <v>996</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="15"/>
@@ -11738,7 +11828,7 @@
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9"/>
       <c r="B62" s="10" t="s">
-        <v>994</v>
+        <v>997</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="15"/>
@@ -11748,13 +11838,13 @@
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9"/>
       <c r="B63" s="10" t="s">
         <v>552</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="D63" s="15"/>
       <c r="E63" s="13"/>
@@ -11768,20 +11858,20 @@
         <v>561</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
       <c r="F64" s="8"/>
     </row>
-    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9"/>
       <c r="B65" s="10" t="s">
-        <v>997</v>
+        <v>1000</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>998</v>
+        <v>1001</v>
       </c>
       <c r="D65" s="15"/>
       <c r="E65" s="13"/>
@@ -11790,13 +11880,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9"/>
       <c r="B66" s="10" t="s">
         <v>562</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>999</v>
+        <v>1002</v>
       </c>
       <c r="D66" s="15"/>
       <c r="E66" s="13"/>
@@ -11805,13 +11895,13 @@
         <v/>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9"/>
       <c r="B67" s="10" t="s">
-        <v>1000</v>
+        <v>1003</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="D67" s="15"/>
       <c r="E67" s="13"/>
@@ -11994,20 +12084,20 @@
         <v>22</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
     </row>
-    <row r="3" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
         <v>574</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="13"/>
@@ -12016,13 +12106,13 @@
         <v/>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
-        <v>1004</v>
+        <v>1007</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="13"/>
@@ -12034,7 +12124,7 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="15"/>
@@ -12047,7 +12137,7 @@
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
-        <v>1007</v>
+        <v>1010</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="15"/>
@@ -12060,7 +12150,7 @@
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="15"/>
@@ -12072,23 +12162,23 @@
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1009</v>
+        <v>1012</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9"/>
       <c r="B9" s="10" t="s">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1012</v>
+        <v>1015</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>
@@ -12097,13 +12187,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
       <c r="B10" s="10" t="s">
-        <v>1013</v>
+        <v>1016</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1014</v>
+        <v>1017</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
@@ -12112,13 +12202,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9"/>
       <c r="B11" s="10" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>
@@ -12127,13 +12217,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9"/>
       <c r="B12" s="10" t="s">
         <v>606</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1017</v>
+        <v>1020</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>
@@ -12142,13 +12232,13 @@
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
-        <v>1018</v>
+        <v>1021</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1019</v>
+        <v>1022</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>
@@ -12157,13 +12247,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>1020</v>
+        <v>1023</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1021</v>
+        <v>1024</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>
@@ -12175,7 +12265,7 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9"/>
       <c r="B15" s="10" t="s">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="15"/>
@@ -12188,7 +12278,7 @@
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9"/>
       <c r="B16" s="10" t="s">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="15"/>
@@ -12203,20 +12293,20 @@
         <v>262</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
       <c r="E17" s="8"/>
       <c r="F17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9"/>
       <c r="B18" s="10" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1026</v>
+        <v>1029</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="13"/>
@@ -12225,13 +12315,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9"/>
       <c r="B19" s="10" t="s">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="13"/>
@@ -12243,7 +12333,7 @@
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
-        <v>1029</v>
+        <v>1032</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="15"/>
@@ -12253,13 +12343,13 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9"/>
       <c r="B21" s="10" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="13"/>
@@ -12268,13 +12358,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9"/>
       <c r="B22" s="10" t="s">
         <v>953</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="13"/>
@@ -12296,13 +12386,13 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9"/>
       <c r="B24" s="10" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="13"/>
@@ -12313,23 +12403,23 @@
     </row>
     <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
       <c r="F25" s="8"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9"/>
       <c r="B26" s="10" t="s">
-        <v>1037</v>
+        <v>1040</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1038</v>
+        <v>1041</v>
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="13"/>
@@ -12338,13 +12428,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9"/>
       <c r="B27" s="10" t="s">
-        <v>1039</v>
+        <v>1042</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1040</v>
+        <v>1043</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="13"/>
@@ -12356,7 +12446,7 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9"/>
       <c r="B28" s="10" t="s">
-        <v>1041</v>
+        <v>1044</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="15"/>
@@ -12366,13 +12456,13 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9"/>
       <c r="B29" s="10" t="s">
-        <v>1042</v>
+        <v>1045</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="13"/>
@@ -12384,7 +12474,7 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9"/>
       <c r="B30" s="10" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="15"/>
@@ -12397,7 +12487,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9"/>
       <c r="B31" s="10" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="15"/>
@@ -12407,13 +12497,13 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9"/>
       <c r="B32" s="10" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="D32" s="15"/>
       <c r="E32" s="13"/>
@@ -12425,7 +12515,7 @@
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9"/>
       <c r="B33" s="10" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="15"/>
@@ -12438,7 +12528,7 @@
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9"/>
       <c r="B34" s="10" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="15"/>
@@ -12448,13 +12538,13 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9"/>
       <c r="B35" s="10" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="13"/>
@@ -12466,7 +12556,7 @@
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9"/>
       <c r="B36" s="10" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="15"/>
@@ -12476,13 +12566,13 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9"/>
       <c r="B37" s="10" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="D37" s="15"/>
       <c r="E37" s="13"/>
@@ -12494,7 +12584,7 @@
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9"/>
       <c r="B38" s="10" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="15"/>
@@ -12509,20 +12599,20 @@
         <v>706</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
     </row>
-    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9"/>
       <c r="B40" s="10" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D40" s="15"/>
       <c r="E40" s="13"/>
@@ -12531,13 +12621,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9"/>
       <c r="B41" s="10" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="D41" s="15"/>
       <c r="E41" s="13"/>
@@ -12549,7 +12639,7 @@
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9"/>
       <c r="B42" s="10" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="15"/>
@@ -12559,13 +12649,13 @@
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9"/>
       <c r="B43" s="10" t="s">
         <v>716</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="D43" s="15"/>
       <c r="E43" s="13"/>
@@ -12579,20 +12669,20 @@
         <v>720</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
       <c r="F44" s="8"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9"/>
       <c r="B45" s="10" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="13"/>
@@ -12601,13 +12691,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9"/>
       <c r="B46" s="10" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="D46" s="15"/>
       <c r="E46" s="13"/>
@@ -12619,7 +12709,7 @@
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9"/>
       <c r="B47" s="10" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="15"/>
@@ -12632,7 +12722,7 @@
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9"/>
       <c r="B48" s="10" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="15"/>
@@ -12642,13 +12732,13 @@
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9"/>
       <c r="B49" s="10" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="13"/>
@@ -12660,7 +12750,7 @@
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9"/>
       <c r="B50" s="10" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="15"/>
@@ -12673,7 +12763,7 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9"/>
       <c r="B51" s="10" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="15"/>
@@ -12685,23 +12775,23 @@
     </row>
     <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
       <c r="E52" s="8"/>
       <c r="F52" s="8"/>
     </row>
-    <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9"/>
       <c r="B53" s="10" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="D53" s="15"/>
       <c r="E53" s="13"/>
@@ -12710,13 +12800,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9"/>
       <c r="B54" s="10" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="13"/>
@@ -12728,7 +12818,7 @@
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9"/>
       <c r="B55" s="10" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="15"/>
@@ -12741,7 +12831,7 @@
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9"/>
       <c r="B56" s="10" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="15"/>
@@ -12754,7 +12844,7 @@
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9"/>
       <c r="B57" s="10" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="15"/>
@@ -12764,13 +12854,13 @@
         <v/>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9"/>
       <c r="B58" s="10" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="D58" s="15"/>
       <c r="E58" s="13"/>
@@ -12782,7 +12872,7 @@
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9"/>
       <c r="B59" s="10" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="15"/>
@@ -12795,7 +12885,7 @@
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9"/>
       <c r="B60" s="10" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="15"/>
@@ -12810,20 +12900,20 @@
         <v>792</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
       <c r="F61" s="8"/>
     </row>
-    <row r="62" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9"/>
       <c r="B62" s="10" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="D62" s="15"/>
       <c r="E62" s="13"/>
@@ -12832,13 +12922,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9"/>
       <c r="B63" s="10" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="D63" s="15"/>
       <c r="E63" s="13"/>
@@ -12850,7 +12940,7 @@
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9"/>
       <c r="B64" s="10" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="15"/>
@@ -12860,13 +12950,13 @@
         <v/>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9"/>
       <c r="B65" s="10" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="D65" s="15"/>
       <c r="E65" s="13"/>
@@ -12878,7 +12968,7 @@
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9"/>
       <c r="B66" s="10" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="15"/>
@@ -12890,23 +12980,23 @@
     </row>
     <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
       <c r="F67" s="8"/>
     </row>
-    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9"/>
       <c r="B68" s="10" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="D68" s="15"/>
       <c r="E68" s="13"/>
@@ -12915,13 +13005,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9"/>
       <c r="B69" s="10" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="D69" s="15"/>
       <c r="E69" s="13"/>
@@ -12933,7 +13023,7 @@
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9"/>
       <c r="B70" s="10" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="15"/>
@@ -12946,7 +13036,7 @@
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="9"/>
       <c r="B71" s="10" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="15"/>
@@ -12956,13 +13046,13 @@
         <v/>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9"/>
       <c r="B72" s="10" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="D72" s="15"/>
       <c r="E72" s="13"/>
@@ -12974,7 +13064,7 @@
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9"/>
       <c r="B73" s="10" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="15"/>
@@ -12987,7 +13077,7 @@
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="9"/>
       <c r="B74" s="10" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="15"/>
@@ -13000,7 +13090,7 @@
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9"/>
       <c r="B75" s="10" t="s">
-        <v>1108</v>
+        <v>1111</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="15"/>
@@ -13010,13 +13100,13 @@
         <v/>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="9"/>
       <c r="B76" s="10" t="s">
         <v>844</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1109</v>
+        <v>1112</v>
       </c>
       <c r="D76" s="15"/>
       <c r="E76" s="13"/>
@@ -13030,20 +13120,20 @@
         <v>860</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
     </row>
-    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="9"/>
       <c r="B78" s="10" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="D78" s="15"/>
       <c r="E78" s="13"/>
@@ -13055,7 +13145,7 @@
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="9"/>
       <c r="B79" s="10" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="15"/>
@@ -13068,7 +13158,7 @@
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="9"/>
       <c r="B80" s="10" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="15"/>
@@ -13081,7 +13171,7 @@
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="9"/>
       <c r="B81" s="10" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="15"/>
@@ -13096,20 +13186,20 @@
         <v>874</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
       <c r="E82" s="8"/>
       <c r="F82" s="8"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="9"/>
       <c r="B83" s="10" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="D83" s="15"/>
       <c r="E83" s="13"/>
@@ -13121,7 +13211,7 @@
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9"/>
       <c r="B84" s="10" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="15"/>
@@ -13134,7 +13224,7 @@
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9"/>
       <c r="B85" s="10" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="15"/>
@@ -13149,20 +13239,20 @@
         <v>890</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
       <c r="E86" s="8"/>
       <c r="F86" s="8"/>
     </row>
-    <row r="87" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="9"/>
       <c r="B87" s="10" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>1123</v>
+        <v>1126</v>
       </c>
       <c r="D87" s="15"/>
       <c r="E87" s="13"/>
@@ -13174,7 +13264,7 @@
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="9"/>
       <c r="B88" s="10" t="s">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="15"/>
@@ -13187,7 +13277,7 @@
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="9"/>
       <c r="B89" s="10" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="15"/>
@@ -13200,7 +13290,7 @@
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="9"/>
       <c r="B90" s="10" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="15"/>
@@ -13210,13 +13300,13 @@
         <v/>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="9"/>
       <c r="B91" s="10" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="D91" s="15"/>
       <c r="E91" s="13"/>
@@ -13228,7 +13318,7 @@
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9"/>
       <c r="B92" s="10" t="s">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="15"/>
@@ -13369,12 +13459,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>1130</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="619.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13461,12 +13551,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>1132</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>1131</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="619.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13579,13 +13669,13 @@
         <v>15</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1135</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13596,13 +13686,13 @@
         <v>22</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>913</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1137</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13613,13 +13703,13 @@
         <v>144</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1138</v>
+        <v>1141</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>934</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13630,13 +13720,13 @@
         <v>262</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>948</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13647,13 +13737,13 @@
         <v>315</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>963</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>1143</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13664,13 +13754,13 @@
         <v>506</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>1145</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13681,13 +13771,13 @@
         <v>533</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>990</v>
+        <v>993</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13698,13 +13788,13 @@
         <v>561</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13715,13 +13805,13 @@
         <v>22</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13732,13 +13822,13 @@
         <v>605</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1010</v>
+        <v>1013</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13749,13 +13839,13 @@
         <v>262</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13766,13 +13856,13 @@
         <v>643</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13783,13 +13873,13 @@
         <v>706</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1159</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13800,13 +13890,13 @@
         <v>720</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>1160</v>
+        <v>1163</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1161</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13817,13 +13907,13 @@
         <v>748</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1163</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13834,13 +13924,13 @@
         <v>792</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1165</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13851,13 +13941,13 @@
         <v>810</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1167</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13868,13 +13958,13 @@
         <v>860</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13885,13 +13975,13 @@
         <v>874</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1171</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13902,13 +13992,13 @@
         <v>890</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1173</v>
+        <v>1176</v>
       </c>
     </row>
   </sheetData>

--- a/ai-training-prompt-engineering/deliverables/Prompt_Template_Configurator.xlsx
+++ b/ai-training-prompt-engineering/deliverables/Prompt_Template_Configurator.xlsx
@@ -17,32 +17,32 @@
     <sheet name="Taxonomy" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="DV_a_a_checks_hard" vbProcedure="false">Options!$D$231:$D$240</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_checks_soft" vbProcedure="false">Options!$D$241:$D$244</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_context_glossary" vbProcedure="false">Options!$D$193:$D$193</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_context_quirks" vbProcedure="false">Options!$D$194:$D$197</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_environment_boundaries" vbProcedure="false">Options!$D$198:$D$200</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_environment_confidentiality" vbProcedure="false">Options!$D$212:$D$214</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_environment_risk_policy" vbProcedure="false">Options!$D$215:$D$217</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_environment_tools_allowed" vbProcedure="false">Options!$D$201:$D$205</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_environment_tools_forbidden" vbProcedure="false">Options!$D$206:$D$211</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_inputs_trust" vbProcedure="false">Options!$D$218:$D$220</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_inputs_unknown_rule" vbProcedure="false">Options!$D$221:$D$221</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_mission_cadence" vbProcedure="false">Options!$D$186:$D$187</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_mission_verification" vbProcedure="false">Options!$D$188:$D$192</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_outputs_logs" vbProcedure="false">Options!$D$245:$D$247</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_outputs_repro" vbProcedure="false">Options!$D$248:$D$250</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_plan_methods_allowed" vbProcedure="false">Options!$D$222:$D$226</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_plan_methods_forbidden" vbProcedure="false">Options!$D$227:$D$230</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_process_autonomy" vbProcedure="false">Options!$D$256:$D$262</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_process_autonomy_level" vbProcedure="false">Options!$D$263:$D$267</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_process_gates" vbProcedure="false">Options!$D$251:$D$255</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_quality_checklist" vbProcedure="false">Options!$D$274:$D$279</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_reporting_discipline" vbProcedure="false">Options!$D$286:$D$287</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_reporting_shape" vbProcedure="false">Options!$D$280:$D$285</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_role_posture" vbProcedure="false">Options!$D$175:$D$179</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_role_standing_behaviors" vbProcedure="false">Options!$D$180:$D$185</definedName>
-    <definedName function="false" hidden="false" name="DV_a_a_rules_invariants" vbProcedure="false">Options!$D$268:$D$273</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_checks_hard" vbProcedure="false">Options!$D$232:$D$241</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_checks_soft" vbProcedure="false">Options!$D$242:$D$245</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_context_glossary" vbProcedure="false">Options!$D$194:$D$194</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_context_quirks" vbProcedure="false">Options!$D$195:$D$198</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_environment_boundaries" vbProcedure="false">Options!$D$199:$D$201</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_environment_confidentiality" vbProcedure="false">Options!$D$213:$D$215</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_environment_risk_policy" vbProcedure="false">Options!$D$216:$D$218</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_environment_tools_allowed" vbProcedure="false">Options!$D$202:$D$206</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_environment_tools_forbidden" vbProcedure="false">Options!$D$207:$D$212</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_inputs_trust" vbProcedure="false">Options!$D$219:$D$221</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_inputs_unknown_rule" vbProcedure="false">Options!$D$222:$D$222</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_mission_cadence" vbProcedure="false">Options!$D$187:$D$188</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_mission_verification" vbProcedure="false">Options!$D$189:$D$193</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_outputs_logs" vbProcedure="false">Options!$D$246:$D$248</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_outputs_repro" vbProcedure="false">Options!$D$249:$D$251</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_plan_methods_allowed" vbProcedure="false">Options!$D$223:$D$227</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_plan_methods_forbidden" vbProcedure="false">Options!$D$228:$D$231</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_process_autonomy" vbProcedure="false">Options!$D$257:$D$263</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_process_autonomy_level" vbProcedure="false">Options!$D$264:$D$268</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_process_gates" vbProcedure="false">Options!$D$252:$D$256</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_quality_checklist" vbProcedure="false">Options!$D$275:$D$280</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_reporting_discipline" vbProcedure="false">Options!$D$287:$D$288</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_reporting_shape" vbProcedure="false">Options!$D$281:$D$286</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_role_posture" vbProcedure="false">Options!$D$176:$D$180</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_role_standing_behaviors" vbProcedure="false">Options!$D$181:$D$186</definedName>
+    <definedName function="false" hidden="false" name="DV_a_a_rules_invariants" vbProcedure="false">Options!$D$269:$D$274</definedName>
     <definedName function="false" hidden="false" name="DV_g_context_constraints" vbProcedure="false">Options!$D$88:$D$92</definedName>
     <definedName function="false" hidden="false" name="DV_g_context_glossary" vbProcedure="false">Options!$D$80:$D$80</definedName>
     <definedName function="false" hidden="false" name="DV_g_context_material" vbProcedure="false">Options!$D$77:$D$79</definedName>
@@ -70,9 +70,9 @@
     <definedName function="false" hidden="false" name="DV_g_task_audience_time_budget" vbProcedure="false">Options!$D$62:$D$64</definedName>
     <definedName function="false" hidden="false" name="DV_g_task_sense_check" vbProcedure="false">Options!$D$74:$D$76</definedName>
     <definedName function="false" hidden="false" name="DV_g_task_success" vbProcedure="false">Options!$D$70:$D$73</definedName>
-    <definedName function="false" hidden="false" name="DV_g_the_out_behavior" vbProcedure="false">Options!$D$168:$D$170</definedName>
+    <definedName function="false" hidden="false" name="DV_g_the_out_behavior" vbProcedure="false">Options!$D$168:$D$171</definedName>
     <definedName function="false" hidden="false" name="DV_g_the_out_triggers" vbProcedure="false">Options!$D$162:$D$167</definedName>
-    <definedName function="false" hidden="false" name="DV_g_the_stop_stop_rule" vbProcedure="false">Options!$D$171:$D$174</definedName>
+    <definedName function="false" hidden="false" name="DV_g_the_stop_stop_rule" vbProcedure="false">Options!$D$172:$D$175</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2397" uniqueCount="1177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="1181">
   <si>
     <t xml:space="preserve">Prompt Template Configurator</t>
   </si>
@@ -1745,7 +1745,19 @@
     <t xml:space="preserve">What to do instead</t>
   </si>
   <si>
+    <t xml:space="preserve">UNKNOWN + gap list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">the checkable default — condition, honest move, and surfacing in one sentence (the course anatomy's form)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anything the material doesn't state: write UNKNOWN — never estimate. List the gaps at the end.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Say so plainly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lightest form — names no output shape</t>
   </si>
   <si>
     <t xml:space="preserve">When uncertain: say "I don't know" or "the material doesn't say" — plainly, without apology.</t>
@@ -3096,7 +3108,7 @@
 WHY IT MATTERS: Models imitate surface detail as much as structure — a real (redacted) example carries your house style's actual distribution; an invented one carries what the model guesses your style is. Exemplar quality and similarity are measured few-shot design decisions. (Prompt Report §2.2)</t>
   </si>
   <si>
-    <t xml:space="preserve">Permission to not know — re-opens the abstain option that benchmark training closed.</t>
+    <t xml:space="preserve">The escape route for missing information: name the condition, the honest move, and how gaps surface — so the model never has to choose between obeying you and being honest.</t>
   </si>
   <si>
     <t xml:space="preserve">When it applies · choice 1</t>
@@ -3113,7 +3125,7 @@
   </si>
   <si>
     <t xml:space="preserve">The escape hatch's shape.
-WHY IT MATTERS: Explicitly permitting 'I don't know' 'can drastically reduce false information' — the vendor's own wording. Giving the escape hatch a shape (say so, ask, or flag and continue) converts invisible guesses into visible, handleable items. (Anthropic reduce-hallucinations, verbatim)</t>
+WHY IT MATTERS: Explicitly permitting 'I don't know' 'can drastically reduce false information' — the vendor's own wording. Prefer a CHECKABLE shape: UNKNOWN plus a gap list can be verified in the output; a bare 'say so' names no form. Giving the escape hatch a shape converts invisible guesses into visible, handleable items. (Anthropic reduce-hallucinations, verbatim)</t>
   </si>
   <si>
     <t xml:space="preserve">The scope boundary — converts open-ended capability into bounded work.</t>
@@ -4313,7 +4325,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G287"/>
+  <dimension ref="A1:G288"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -8166,7 +8178,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="5" t="s">
         <v>21</v>
       </c>
@@ -8180,10 +8192,10 @@
         <v>553</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>464</v>
+        <v>554</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="G168" s="5" t="s">
         <v>27</v>
@@ -8200,13 +8212,13 @@
         <v>552</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="G169" s="5" t="s">
         <v>27</v>
@@ -8223,13 +8235,13 @@
         <v>552</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F170" s="5" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="G170" s="5" t="s">
         <v>27</v>
@@ -8240,16 +8252,16 @@
         <v>21</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>561</v>
+        <v>533</v>
       </c>
       <c r="C171" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="D171" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="D171" s="5" t="s">
+      <c r="E171" s="5" t="s">
         <v>563</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>244</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>564</v>
@@ -8263,19 +8275,19 @@
         <v>21</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>189</v>
+        <v>244</v>
       </c>
       <c r="F172" s="5" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G172" s="5" t="s">
         <v>27</v>
@@ -8286,19 +8298,19 @@
         <v>21</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>568</v>
+        <v>189</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="G173" s="5" t="s">
         <v>27</v>
@@ -8309,65 +8321,65 @@
         <v>21</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G174" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="5" t="s">
-        <v>573</v>
+        <v>21</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>22</v>
+        <v>565</v>
       </c>
       <c r="C175" s="5" t="s">
+        <v>566</v>
+      </c>
+      <c r="D175" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="D175" s="5" t="s">
+      <c r="E175" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="E175" s="5" t="s">
+      <c r="F175" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="F175" s="5" t="s">
+      <c r="G175" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="5" t="s">
         <v>577</v>
-      </c>
-      <c r="G175" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A176" s="5" t="s">
-        <v>573</v>
       </c>
       <c r="B176" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F176" s="5" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="G176" s="5" t="s">
         <v>27</v>
@@ -8375,22 +8387,22 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F177" s="5" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G177" s="5" t="s">
         <v>27</v>
@@ -8398,22 +8410,22 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="F178" s="5" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="G178" s="5" t="s">
         <v>27</v>
@@ -8421,68 +8433,68 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="G179" s="5" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B180" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>590</v>
+        <v>578</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>84</v>
+        <v>591</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>519</v>
+        <v>592</v>
       </c>
       <c r="F180" s="5" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G180" s="5" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>592</v>
+        <v>84</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>593</v>
+        <v>519</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G181" s="5" t="s">
         <v>27</v>
@@ -8490,22 +8502,22 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="G182" s="5" t="s">
         <v>27</v>
@@ -8513,22 +8525,22 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="G183" s="5" t="s">
         <v>27</v>
@@ -8536,22 +8548,22 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>519</v>
+        <v>603</v>
       </c>
       <c r="F184" s="5" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="G184" s="5" t="s">
         <v>27</v>
@@ -8559,22 +8571,22 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="E185" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F185" s="5" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="G185" s="5" t="s">
         <v>27</v>
@@ -8582,68 +8594,68 @@
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>605</v>
+        <v>22</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>606</v>
+        <v>594</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>607</v>
       </c>
       <c r="E186" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="F186" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="F186" s="5" t="s">
+      <c r="G186" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B187" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="G186" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="187" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="B187" s="5" t="s">
-        <v>605</v>
-      </c>
       <c r="C187" s="5" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D187" s="5" t="s">
+        <v>611</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>612</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="G187" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C188" s="5" t="s">
         <v>610</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>611</v>
-      </c>
-      <c r="F187" s="5" t="s">
-        <v>612</v>
-      </c>
-      <c r="G187" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="B188" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="C188" s="5" t="s">
-        <v>613</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>614</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>593</v>
+        <v>615</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="G188" s="5" t="s">
         <v>27</v>
@@ -8651,22 +8663,22 @@
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="G189" s="5" t="s">
         <v>27</v>
@@ -8674,22 +8686,22 @@
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="F190" s="5" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="G190" s="5" t="s">
         <v>27</v>
@@ -8697,22 +8709,22 @@
     </row>
     <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="G191" s="5" t="s">
         <v>27</v>
@@ -8720,68 +8732,68 @@
     </row>
     <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="F192" s="5" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="G192" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>609</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>617</v>
+      </c>
+      <c r="D193" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="E193" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="F193" s="5" t="s">
+        <v>631</v>
+      </c>
+      <c r="G193" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="B193" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C193" s="5" t="s">
-        <v>628</v>
-      </c>
-      <c r="D193" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="E193" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="F193" s="5" t="s">
-        <v>630</v>
-      </c>
-      <c r="G193" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>262</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>277</v>
+        <v>632</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>631</v>
+        <v>274</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="F194" s="5" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="G194" s="5" t="s">
         <v>27</v>
@@ -8789,7 +8801,7 @@
     </row>
     <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>262</v>
@@ -8798,13 +8810,13 @@
         <v>277</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="F195" s="5" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G195" s="5" t="s">
         <v>27</v>
@@ -8812,7 +8824,7 @@
     </row>
     <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>262</v>
@@ -8821,21 +8833,21 @@
         <v>277</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="F196" s="5" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="G196" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B197" s="5" t="s">
         <v>262</v>
@@ -8844,82 +8856,82 @@
         <v>277</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="F197" s="5" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="G197" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>643</v>
+        <v>262</v>
       </c>
       <c r="C198" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="D198" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="D198" s="5" t="s">
+      <c r="E198" s="5" t="s">
         <v>645</v>
-      </c>
-      <c r="E198" s="5" t="s">
-        <v>519</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>646</v>
       </c>
       <c r="G198" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="199" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="E199" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F199" s="5" t="s">
+        <v>650</v>
+      </c>
+      <c r="G199" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C200" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="G199" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="B200" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="C200" s="5" t="s">
-        <v>644</v>
-      </c>
       <c r="D200" s="5" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>650</v>
+        <v>519</v>
       </c>
       <c r="F200" s="5" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="G200" s="5" t="s">
         <v>27</v>
@@ -8927,13 +8939,13 @@
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A201" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D201" s="5" t="s">
         <v>653</v>
@@ -8950,22 +8962,22 @@
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="F202" s="5" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="G202" s="5" t="s">
         <v>27</v>
@@ -8973,22 +8985,22 @@
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="F203" s="5" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G203" s="5" t="s">
         <v>27</v>
@@ -8996,22 +9008,22 @@
     </row>
     <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A204" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="F204" s="5" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G204" s="5" t="s">
         <v>27</v>
@@ -9019,36 +9031,36 @@
     </row>
     <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="F205" s="5" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G205" s="5" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>668</v>
+        <v>656</v>
       </c>
       <c r="D206" s="5" t="s">
         <v>669</v>
@@ -9060,27 +9072,27 @@
         <v>671</v>
       </c>
       <c r="G206" s="5" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="G207" s="5" t="s">
         <v>27</v>
@@ -9088,22 +9100,22 @@
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>519</v>
+        <v>677</v>
       </c>
       <c r="F208" s="5" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="G208" s="5" t="s">
         <v>27</v>
@@ -9111,22 +9123,22 @@
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>678</v>
+        <v>519</v>
       </c>
       <c r="F209" s="5" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="G209" s="5" t="s">
         <v>27</v>
@@ -9134,22 +9146,22 @@
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A210" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="F210" s="5" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="G210" s="5" t="s">
         <v>27</v>
@@ -9157,36 +9169,36 @@
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="F211" s="5" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="G211" s="5" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A212" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>686</v>
+        <v>672</v>
       </c>
       <c r="D212" s="5" t="s">
         <v>687</v>
@@ -9198,27 +9210,27 @@
         <v>689</v>
       </c>
       <c r="G212" s="5" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A213" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="G213" s="5" t="s">
         <v>27</v>
@@ -9226,36 +9238,36 @@
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A214" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="F214" s="5" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G214" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D215" s="5" t="s">
         <v>697</v>
@@ -9272,22 +9284,22 @@
     </row>
     <row r="216" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A216" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="F216" s="5" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G216" s="5" t="s">
         <v>27</v>
@@ -9295,68 +9307,68 @@
     </row>
     <row r="217" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A217" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="F217" s="5" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="G217" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>700</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>707</v>
+      </c>
+      <c r="E218" s="5" t="s">
+        <v>708</v>
+      </c>
+      <c r="F218" s="5" t="s">
+        <v>709</v>
+      </c>
+      <c r="G218" s="5" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="B218" s="5" t="s">
-        <v>706</v>
-      </c>
-      <c r="C218" s="5" t="s">
-        <v>707</v>
-      </c>
-      <c r="D218" s="5" t="s">
-        <v>708</v>
-      </c>
-      <c r="E218" s="5" t="s">
-        <v>709</v>
-      </c>
-      <c r="F218" s="5" t="s">
-        <v>710</v>
-      </c>
-      <c r="G218" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>27</v>
@@ -9364,39 +9376,39 @@
     </row>
     <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="D220" s="5" t="s">
+        <v>715</v>
+      </c>
+      <c r="E220" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="F220" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="G220" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>711</v>
+      </c>
+      <c r="D221" s="5" t="s">
         <v>290</v>
-      </c>
-      <c r="E220" s="5" t="s">
-        <v>714</v>
-      </c>
-      <c r="F220" s="5" t="s">
-        <v>715</v>
-      </c>
-      <c r="G220" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="221" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="B221" s="5" t="s">
-        <v>706</v>
-      </c>
-      <c r="C221" s="5" t="s">
-        <v>716</v>
-      </c>
-      <c r="D221" s="5" t="s">
-        <v>717</v>
       </c>
       <c r="E221" s="5" t="s">
         <v>718</v>
@@ -9408,24 +9420,24 @@
         <v>27</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B222" s="5" t="s">
+        <v>710</v>
+      </c>
+      <c r="C222" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="C222" s="5" t="s">
+      <c r="D222" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="D222" s="5" t="s">
+      <c r="E222" s="5" t="s">
         <v>722</v>
       </c>
-      <c r="E222" s="5" t="s">
+      <c r="F222" s="5" t="s">
         <v>723</v>
-      </c>
-      <c r="F222" s="5" t="s">
-        <v>724</v>
       </c>
       <c r="G222" s="5" t="s">
         <v>27</v>
@@ -9433,22 +9445,22 @@
     </row>
     <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="F223" s="5" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G223" s="5" t="s">
         <v>27</v>
@@ -9456,22 +9468,22 @@
     </row>
     <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="F224" s="5" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="G224" s="5" t="s">
         <v>27</v>
@@ -9479,22 +9491,22 @@
     </row>
     <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="F225" s="5" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="G225" s="5" t="s">
         <v>27</v>
@@ -9502,22 +9514,22 @@
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="F226" s="5" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="G226" s="5" t="s">
         <v>27</v>
@@ -9525,13 +9537,13 @@
     </row>
     <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>737</v>
+        <v>725</v>
       </c>
       <c r="D227" s="5" t="s">
         <v>738</v>
@@ -9548,22 +9560,22 @@
     </row>
     <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="G228" s="5" t="s">
         <v>27</v>
@@ -9571,22 +9583,22 @@
     </row>
     <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>519</v>
+        <v>746</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="G229" s="5" t="s">
         <v>27</v>
@@ -9594,22 +9606,22 @@
     </row>
     <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="E230" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="G230" s="5" t="s">
         <v>27</v>
@@ -9617,22 +9629,22 @@
     </row>
     <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>749</v>
+        <v>741</v>
       </c>
       <c r="D231" s="5" t="s">
         <v>750</v>
       </c>
       <c r="E231" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="F231" s="5" t="s">
         <v>751</v>
-      </c>
-      <c r="F231" s="5" t="s">
-        <v>752</v>
       </c>
       <c r="G231" s="5" t="s">
         <v>27</v>
@@ -9640,22 +9652,22 @@
     </row>
     <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>519</v>
+        <v>755</v>
       </c>
       <c r="F232" s="5" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="G232" s="5" t="s">
         <v>27</v>
@@ -9663,22 +9675,22 @@
     </row>
     <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>756</v>
+        <v>519</v>
       </c>
       <c r="F233" s="5" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="G233" s="5" t="s">
         <v>27</v>
@@ -9686,22 +9698,22 @@
     </row>
     <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="F234" s="5" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="G234" s="5" t="s">
         <v>27</v>
@@ -9709,22 +9721,22 @@
     </row>
     <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="F235" s="5" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="G235" s="5" t="s">
         <v>27</v>
@@ -9732,22 +9744,22 @@
     </row>
     <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="F236" s="5" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="G236" s="5" t="s">
         <v>27</v>
@@ -9755,105 +9767,105 @@
     </row>
     <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="F237" s="5" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="238" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F238" s="5" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G238" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="F239" s="5" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="G239" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G240" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>779</v>
+        <v>753</v>
       </c>
       <c r="D241" s="5" t="s">
         <v>780</v>
@@ -9865,27 +9877,27 @@
         <v>782</v>
       </c>
       <c r="G241" s="5" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="F242" s="5" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="G242" s="5" t="s">
         <v>27</v>
@@ -9893,22 +9905,22 @@
     </row>
     <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A243" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F243" s="5" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G243" s="5" t="s">
         <v>27</v>
@@ -9916,22 +9928,22 @@
     </row>
     <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="F244" s="5" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="G244" s="5" t="s">
         <v>27</v>
@@ -9939,19 +9951,19 @@
     </row>
     <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>792</v>
+        <v>752</v>
       </c>
       <c r="C245" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="D245" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="D245" s="5" t="s">
+      <c r="E245" s="5" t="s">
         <v>794</v>
-      </c>
-      <c r="E245" s="5" t="s">
-        <v>519</v>
       </c>
       <c r="F245" s="5" t="s">
         <v>795</v>
@@ -9962,22 +9974,22 @@
     </row>
     <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A246" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>244</v>
+        <v>519</v>
       </c>
       <c r="F246" s="5" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="G246" s="5" t="s">
         <v>27</v>
@@ -9985,22 +9997,22 @@
     </row>
     <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>519</v>
+        <v>244</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="G247" s="5" t="s">
         <v>27</v>
@@ -10008,19 +10020,19 @@
     </row>
     <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>802</v>
+        <v>519</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>803</v>
@@ -10031,22 +10043,22 @@
     </row>
     <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="G249" s="5" t="s">
         <v>27</v>
@@ -10054,68 +10066,68 @@
     </row>
     <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G250" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A251" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>796</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="D251" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="F251" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="G251" s="5" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="B251" s="5" t="s">
-        <v>810</v>
-      </c>
-      <c r="C251" s="5" t="s">
-        <v>811</v>
-      </c>
-      <c r="D251" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="E251" s="5" t="s">
-        <v>813</v>
-      </c>
-      <c r="F251" s="5" t="s">
+    <row r="252" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A252" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B252" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="G251" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="B252" s="5" t="s">
-        <v>810</v>
-      </c>
       <c r="C252" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>593</v>
+        <v>817</v>
       </c>
       <c r="F252" s="5" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="G252" s="5" t="s">
         <v>27</v>
@@ -10123,22 +10135,22 @@
     </row>
     <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>818</v>
+        <v>597</v>
       </c>
       <c r="F253" s="5" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G253" s="5" t="s">
         <v>27</v>
@@ -10146,22 +10158,22 @@
     </row>
     <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="F254" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G254" s="5" t="s">
         <v>27</v>
@@ -10169,36 +10181,36 @@
     </row>
     <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="F255" s="5" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>826</v>
+        <v>815</v>
       </c>
       <c r="D256" s="5" t="s">
         <v>827</v>
@@ -10210,27 +10222,27 @@
         <v>829</v>
       </c>
       <c r="G256" s="5" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="F257" s="5" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="G257" s="5" t="s">
         <v>27</v>
@@ -10238,22 +10250,22 @@
     </row>
     <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D258" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="E258" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="E258" s="5" t="s">
-        <v>828</v>
-      </c>
       <c r="F258" s="5" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="G258" s="5" t="s">
         <v>27</v>
@@ -10261,68 +10273,68 @@
     </row>
     <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="F259" s="5" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="G259" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="G260" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>839</v>
+        <v>832</v>
       </c>
       <c r="F261" s="5" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G261" s="5" t="s">
         <v>27</v>
@@ -10330,36 +10342,36 @@
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="G262" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="263" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>844</v>
+        <v>830</v>
       </c>
       <c r="D263" s="5" t="s">
         <v>845</v>
@@ -10371,27 +10383,27 @@
         <v>847</v>
       </c>
       <c r="G263" s="5" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A264" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="F264" s="5" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G264" s="5" t="s">
         <v>27</v>
@@ -10399,22 +10411,22 @@
     </row>
     <row r="265" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F265" s="5" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="G265" s="5" t="s">
         <v>27</v>
@@ -10422,22 +10434,22 @@
     </row>
     <row r="266" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F266" s="5" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G266" s="5" t="s">
         <v>27</v>
@@ -10445,68 +10457,68 @@
     </row>
     <row r="267" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F267" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G267" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A268" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="D268" s="5" t="s">
+        <v>861</v>
+      </c>
+      <c r="E268" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="F268" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="G268" s="5" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A268" s="5" t="s">
-        <v>573</v>
-      </c>
-      <c r="B268" s="5" t="s">
-        <v>860</v>
-      </c>
-      <c r="C268" s="5" t="s">
-        <v>861</v>
-      </c>
-      <c r="D268" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E268" s="5" t="s">
-        <v>519</v>
-      </c>
-      <c r="F268" s="5" t="s">
-        <v>862</v>
-      </c>
-      <c r="G268" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>863</v>
+        <v>84</v>
       </c>
       <c r="E269" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F269" s="5" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="G269" s="5" t="s">
         <v>27</v>
@@ -10514,22 +10526,22 @@
     </row>
     <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="E270" s="5" t="s">
-        <v>723</v>
+        <v>519</v>
       </c>
       <c r="F270" s="5" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="G270" s="5" t="s">
         <v>27</v>
@@ -10537,22 +10549,22 @@
     </row>
     <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>519</v>
+        <v>727</v>
       </c>
       <c r="F271" s="5" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="G271" s="5" t="s">
         <v>27</v>
@@ -10560,22 +10572,22 @@
     </row>
     <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="E272" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F272" s="5" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="G272" s="5" t="s">
         <v>27</v>
@@ -10583,22 +10595,22 @@
     </row>
     <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>872</v>
+        <v>519</v>
       </c>
       <c r="F273" s="5" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G273" s="5" t="s">
         <v>27</v>
@@ -10606,19 +10618,19 @@
     </row>
     <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
       <c r="C274" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="D274" s="5" t="s">
         <v>875</v>
       </c>
-      <c r="D274" s="5" t="s">
+      <c r="E274" s="5" t="s">
         <v>876</v>
-      </c>
-      <c r="E274" s="5" t="s">
-        <v>519</v>
       </c>
       <c r="F274" s="5" t="s">
         <v>877</v>
@@ -10629,22 +10641,22 @@
     </row>
     <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="E275" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F275" s="5" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="G275" s="5" t="s">
         <v>27</v>
@@ -10652,22 +10664,22 @@
     </row>
     <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>881</v>
+        <v>519</v>
       </c>
       <c r="F276" s="5" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G276" s="5" t="s">
         <v>27</v>
@@ -10675,22 +10687,22 @@
     </row>
     <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>519</v>
+        <v>885</v>
       </c>
       <c r="F277" s="5" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="G277" s="5" t="s">
         <v>27</v>
@@ -10698,91 +10710,91 @@
     </row>
     <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>808</v>
+        <v>519</v>
       </c>
       <c r="F278" s="5" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="G278" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>888</v>
+        <v>812</v>
       </c>
       <c r="F279" s="5" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>890</v>
+        <v>878</v>
       </c>
       <c r="C280" s="5" t="s">
+        <v>879</v>
+      </c>
+      <c r="D280" s="5" t="s">
         <v>891</v>
       </c>
-      <c r="D280" s="5" t="s">
+      <c r="E280" s="5" t="s">
         <v>892</v>
-      </c>
-      <c r="E280" s="5" t="s">
-        <v>519</v>
       </c>
       <c r="F280" s="5" t="s">
         <v>893</v>
       </c>
       <c r="G280" s="5" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="E281" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="G281" s="5" t="s">
         <v>27</v>
@@ -10790,22 +10802,22 @@
     </row>
     <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="E282" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F282" s="5" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="G282" s="5" t="s">
         <v>27</v>
@@ -10813,22 +10825,22 @@
     </row>
     <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="E283" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="G283" s="5" t="s">
         <v>27</v>
@@ -10836,22 +10848,22 @@
     </row>
     <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="E284" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F284" s="5" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G284" s="5" t="s">
         <v>27</v>
@@ -10859,22 +10871,22 @@
     </row>
     <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="E285" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="G285" s="5" t="s">
         <v>27</v>
@@ -10882,22 +10894,22 @@
     </row>
     <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="E286" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F286" s="5" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="G286" s="5" t="s">
         <v>27</v>
@@ -10905,24 +10917,47 @@
     </row>
     <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A287" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="E287" s="5" t="s">
         <v>519</v>
       </c>
       <c r="F287" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="G287" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A288" s="5" t="s">
+        <v>577</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="C288" s="5" t="s">
         <v>908</v>
       </c>
-      <c r="G287" s="5" t="s">
+      <c r="D288" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="E288" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="F288" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="G288" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -10961,16 +10996,16 @@
         <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10978,7 +11013,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -10991,7 +11026,7 @@
         <v>23</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>24</v>
@@ -11005,10 +11040,10 @@
     <row r="4" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="13"/>
@@ -11020,10 +11055,10 @@
     <row r="5" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="13"/>
@@ -11035,7 +11070,7 @@
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="15"/>
@@ -11048,10 +11083,10 @@
     <row r="7" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="D7" s="12" t="s">
         <v>84</v>
@@ -11065,7 +11100,7 @@
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9"/>
       <c r="B8" s="10" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="12"/>
@@ -11078,7 +11113,7 @@
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9"/>
       <c r="B9" s="10" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="12"/>
@@ -11091,10 +11126,10 @@
     <row r="10" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
       <c r="B10" s="10" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
@@ -11106,7 +11141,7 @@
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9"/>
       <c r="B11" s="10" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="15"/>
@@ -11119,7 +11154,7 @@
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9"/>
       <c r="B12" s="10" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="15"/>
@@ -11132,10 +11167,10 @@
     <row r="13" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>
@@ -11147,7 +11182,7 @@
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="15"/>
@@ -11160,7 +11195,7 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9"/>
       <c r="B15" s="10" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="15"/>
@@ -11176,7 +11211,7 @@
         <v>128</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>
@@ -11187,10 +11222,10 @@
     </row>
     <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -11203,7 +11238,7 @@
         <v>145</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="D18" s="12" t="s">
         <v>146</v>
@@ -11217,14 +11252,14 @@
     <row r="19" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9"/>
       <c r="B19" s="10" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="13" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="F19" s="14" t="str">
         <f aca="false">$E19</f>
@@ -11237,7 +11272,7 @@
         <v>194</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="D20" s="15"/>
       <c r="E20" s="13"/>
@@ -11249,10 +11284,10 @@
     <row r="21" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9"/>
       <c r="B21" s="10" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="13"/>
@@ -11264,10 +11299,10 @@
     <row r="22" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9"/>
       <c r="B22" s="10" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="13"/>
@@ -11282,7 +11317,7 @@
         <v>239</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="13"/>
@@ -11294,10 +11329,10 @@
     <row r="24" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9"/>
       <c r="B24" s="10" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="13"/>
@@ -11312,7 +11347,7 @@
         <v>252</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="13"/>
@@ -11326,7 +11361,7 @@
         <v>262</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -11339,7 +11374,7 @@
         <v>263</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="13"/>
@@ -11351,10 +11386,10 @@
     <row r="28" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9"/>
       <c r="B28" s="10" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="D28" s="15"/>
       <c r="E28" s="13"/>
@@ -11366,7 +11401,7 @@
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9"/>
       <c r="B29" s="10" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="15"/>
@@ -11379,10 +11414,10 @@
     <row r="30" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9"/>
       <c r="B30" s="10" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="D30" s="15"/>
       <c r="E30" s="13"/>
@@ -11394,7 +11429,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9"/>
       <c r="B31" s="10" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="15"/>
@@ -11407,7 +11442,7 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9"/>
       <c r="B32" s="10" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="15"/>
@@ -11420,10 +11455,10 @@
     <row r="33" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9"/>
       <c r="B33" s="10" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="D33" s="15"/>
       <c r="E33" s="13"/>
@@ -11435,7 +11470,7 @@
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9"/>
       <c r="B34" s="10" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="15"/>
@@ -11448,7 +11483,7 @@
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9"/>
       <c r="B35" s="10" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="15"/>
@@ -11461,10 +11496,10 @@
     <row r="36" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9"/>
       <c r="B36" s="10" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="D36" s="15"/>
       <c r="E36" s="13"/>
@@ -11478,7 +11513,7 @@
         <v>315</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
@@ -11491,7 +11526,7 @@
         <v>316</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="D38" s="15"/>
       <c r="E38" s="13"/>
@@ -11503,10 +11538,10 @@
     <row r="39" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9"/>
       <c r="B39" s="10" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="D39" s="15"/>
       <c r="E39" s="13"/>
@@ -11518,7 +11553,7 @@
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9"/>
       <c r="B40" s="10" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="15"/>
@@ -11531,7 +11566,7 @@
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9"/>
       <c r="B41" s="10" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="15"/>
@@ -11547,7 +11582,7 @@
         <v>381</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="D42" s="15"/>
       <c r="E42" s="13"/>
@@ -11559,10 +11594,10 @@
     <row r="43" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9"/>
       <c r="B43" s="10" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="D43" s="15"/>
       <c r="E43" s="13"/>
@@ -11574,7 +11609,7 @@
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9"/>
       <c r="B44" s="10" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="15"/>
@@ -11587,10 +11622,10 @@
     <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9"/>
       <c r="B45" s="10" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="13"/>
@@ -11602,10 +11637,10 @@
     <row r="46" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9"/>
       <c r="B46" s="10" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D46" s="15"/>
       <c r="E46" s="13"/>
@@ -11617,10 +11652,10 @@
     <row r="47" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9"/>
       <c r="B47" s="10" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="D47" s="15"/>
       <c r="E47" s="13"/>
@@ -11635,7 +11670,7 @@
         <v>463</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="D48" s="15"/>
       <c r="E48" s="13"/>
@@ -11647,10 +11682,10 @@
     <row r="49" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9"/>
       <c r="B49" s="10" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="13"/>
@@ -11662,7 +11697,7 @@
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9"/>
       <c r="B50" s="10" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="15"/>
@@ -11675,7 +11710,7 @@
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9"/>
       <c r="B51" s="10" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="15"/>
@@ -11691,7 +11726,7 @@
         <v>494</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="D52" s="15"/>
       <c r="E52" s="13"/>
@@ -11705,7 +11740,7 @@
         <v>506</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="C53" s="8"/>
       <c r="D53" s="8"/>
@@ -11718,7 +11753,7 @@
         <v>507</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="13"/>
@@ -11730,10 +11765,10 @@
     <row r="55" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9"/>
       <c r="B55" s="10" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="D55" s="15"/>
       <c r="E55" s="13"/>
@@ -11745,7 +11780,7 @@
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9"/>
       <c r="B56" s="10" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="15"/>
@@ -11761,7 +11796,7 @@
         <v>527</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="D57" s="15"/>
       <c r="E57" s="13"/>
@@ -11773,10 +11808,10 @@
     <row r="58" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9"/>
       <c r="B58" s="10" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="D58" s="15"/>
       <c r="E58" s="13"/>
@@ -11785,12 +11820,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
         <v>533</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="C59" s="8"/>
       <c r="D59" s="8"/>
@@ -11800,10 +11835,10 @@
     <row r="60" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9"/>
       <c r="B60" s="10" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="D60" s="15"/>
       <c r="E60" s="13"/>
@@ -11815,7 +11850,7 @@
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9"/>
       <c r="B61" s="10" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="15"/>
@@ -11828,7 +11863,7 @@
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9"/>
       <c r="B62" s="10" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="15"/>
@@ -11838,27 +11873,27 @@
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9"/>
       <c r="B63" s="10" t="s">
         <v>552</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="D63" s="15"/>
       <c r="E63" s="13"/>
       <c r="F63" s="14" t="str">
-        <f aca="false">IF($E63&lt;&gt;"",$E63,IF($D63="","",IFERROR(INDEX(Options!$F$168:$F$170,MATCH($D63,Options!$D$168:$D$170,0)),"")))</f>
+        <f aca="false">IF($E63&lt;&gt;"",$E63,IF($D63="","",IFERROR(INDEX(Options!$F$168:$F$171,MATCH($D63,Options!$D$168:$D$171,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="64" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C64" s="8"/>
       <c r="D64" s="8"/>
@@ -11868,10 +11903,10 @@
     <row r="65" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9"/>
       <c r="B65" s="10" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="D65" s="15"/>
       <c r="E65" s="13"/>
@@ -11883,25 +11918,25 @@
     <row r="66" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9"/>
       <c r="B66" s="10" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
       <c r="D66" s="15"/>
       <c r="E66" s="13"/>
       <c r="F66" s="14" t="str">
-        <f aca="false">IF($E66&lt;&gt;"",$E66,IF($D66="","",IFERROR(INDEX(Options!$F$171:$F$174,MATCH($D66,Options!$D$171:$D$174,0)),"")))</f>
+        <f aca="false">IF($E66&lt;&gt;"",$E66,IF($D66="","",IFERROR(INDEX(Options!$F$172:$F$175,MATCH($D66,Options!$D$172:$D$175,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="67" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9"/>
       <c r="B67" s="10" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="D67" s="15"/>
       <c r="E67" s="13"/>
@@ -12067,16 +12102,16 @@
         <v>16</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12084,7 +12119,7 @@
         <v>22</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -12094,78 +12129,78 @@
     <row r="3" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9"/>
       <c r="B3" s="10" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="13"/>
       <c r="F3" s="14" t="str">
-        <f aca="false">IF($E3&lt;&gt;"",$E3,IF($D3="","",IFERROR(INDEX(Options!$F$175:$F$179,MATCH($D3,Options!$D$175:$D$179,0)),"")))</f>
+        <f aca="false">IF($E3&lt;&gt;"",$E3,IF($D3="","",IFERROR(INDEX(Options!$F$176:$F$180,MATCH($D3,Options!$D$176:$D$180,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9"/>
       <c r="B4" s="10" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="13"/>
       <c r="F4" s="14" t="str">
-        <f aca="false">IF($E4&lt;&gt;"",$E4,IF($D4="","",IFERROR(INDEX(Options!$F$180:$F$185,MATCH($D4,Options!$D$180:$D$185,0)),"")))</f>
+        <f aca="false">IF($E4&lt;&gt;"",$E4,IF($D4="","",IFERROR(INDEX(Options!$F$181:$F$186,MATCH($D4,Options!$D$181:$D$186,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="15"/>
       <c r="E5" s="13"/>
       <c r="F5" s="14" t="str">
-        <f aca="false">IF($E5&lt;&gt;"",$E5,IF($D5="","",IFERROR(INDEX(Options!$F$180:$F$185,MATCH($D5,Options!$D$180:$D$185,0)),"")))</f>
+        <f aca="false">IF($E5&lt;&gt;"",$E5,IF($D5="","",IFERROR(INDEX(Options!$F$181:$F$186,MATCH($D5,Options!$D$181:$D$186,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9"/>
       <c r="B6" s="10" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="15"/>
       <c r="E6" s="13"/>
       <c r="F6" s="14" t="str">
-        <f aca="false">IF($E6&lt;&gt;"",$E6,IF($D6="","",IFERROR(INDEX(Options!$F$180:$F$185,MATCH($D6,Options!$D$180:$D$185,0)),"")))</f>
+        <f aca="false">IF($E6&lt;&gt;"",$E6,IF($D6="","",IFERROR(INDEX(Options!$F$181:$F$186,MATCH($D6,Options!$D$181:$D$186,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="15"/>
       <c r="E7" s="13"/>
       <c r="F7" s="14" t="str">
-        <f aca="false">IF($E7&lt;&gt;"",$E7,IF($D7="","",IFERROR(INDEX(Options!$F$180:$F$185,MATCH($D7,Options!$D$180:$D$185,0)),"")))</f>
+        <f aca="false">IF($E7&lt;&gt;"",$E7,IF($D7="","",IFERROR(INDEX(Options!$F$181:$F$186,MATCH($D7,Options!$D$181:$D$186,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -12175,10 +12210,10 @@
     <row r="9" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9"/>
       <c r="B9" s="10" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="13"/>
@@ -12190,10 +12225,10 @@
     <row r="10" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9"/>
       <c r="B10" s="10" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="D10" s="15"/>
       <c r="E10" s="13"/>
@@ -12205,10 +12240,10 @@
     <row r="11" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9"/>
       <c r="B11" s="10" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="13"/>
@@ -12220,25 +12255,25 @@
     <row r="12" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9"/>
       <c r="B12" s="10" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="13"/>
       <c r="F12" s="14" t="str">
-        <f aca="false">IF($E12&lt;&gt;"",$E12,IF($D12="","",IFERROR(INDEX(Options!$F$186:$F$187,MATCH($D12,Options!$D$186:$D$187,0)),"")))</f>
+        <f aca="false">IF($E12&lt;&gt;"",$E12,IF($D12="","",IFERROR(INDEX(Options!$F$187:$F$188,MATCH($D12,Options!$D$187:$D$188,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9"/>
       <c r="B13" s="10" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="13"/>
@@ -12250,41 +12285,41 @@
     <row r="14" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="13"/>
       <c r="F14" s="14" t="str">
-        <f aca="false">IF($E14&lt;&gt;"",$E14,IF($D14="","",IFERROR(INDEX(Options!$F$188:$F$192,MATCH($D14,Options!$D$188:$D$192,0)),"")))</f>
+        <f aca="false">IF($E14&lt;&gt;"",$E14,IF($D14="","",IFERROR(INDEX(Options!$F$189:$F$193,MATCH($D14,Options!$D$189:$D$193,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9"/>
       <c r="B15" s="10" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="15"/>
       <c r="E15" s="13"/>
       <c r="F15" s="14" t="str">
-        <f aca="false">IF($E15&lt;&gt;"",$E15,IF($D15="","",IFERROR(INDEX(Options!$F$188:$F$192,MATCH($D15,Options!$D$188:$D$192,0)),"")))</f>
+        <f aca="false">IF($E15&lt;&gt;"",$E15,IF($D15="","",IFERROR(INDEX(Options!$F$189:$F$193,MATCH($D15,Options!$D$189:$D$193,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9"/>
       <c r="B16" s="10" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="15"/>
       <c r="E16" s="13"/>
       <c r="F16" s="14" t="str">
-        <f aca="false">IF($E16&lt;&gt;"",$E16,IF($D16="","",IFERROR(INDEX(Options!$F$188:$F$192,MATCH($D16,Options!$D$188:$D$192,0)),"")))</f>
+        <f aca="false">IF($E16&lt;&gt;"",$E16,IF($D16="","",IFERROR(INDEX(Options!$F$189:$F$193,MATCH($D16,Options!$D$189:$D$193,0)),"")))</f>
         <v/>
       </c>
     </row>
@@ -12293,7 +12328,7 @@
         <v>262</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -12303,10 +12338,10 @@
     <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9"/>
       <c r="B18" s="10" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="13"/>
@@ -12318,38 +12353,38 @@
     <row r="19" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9"/>
       <c r="B19" s="10" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="13"/>
       <c r="F19" s="14" t="str">
-        <f aca="false">IF($E19&lt;&gt;"",$E19,IF($D19="","",IFERROR(INDEX(Options!$F$193:$F$193,MATCH($D19,Options!$D$193:$D$193,0)),"")))</f>
+        <f aca="false">IF($E19&lt;&gt;"",$E19,IF($D19="","",IFERROR(INDEX(Options!$F$194:$F$194,MATCH($D19,Options!$D$194:$D$194,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9"/>
       <c r="B20" s="10" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="15"/>
       <c r="E20" s="13"/>
       <c r="F20" s="14" t="str">
-        <f aca="false">IF($E20&lt;&gt;"",$E20,IF($D20="","",IFERROR(INDEX(Options!$F$193:$F$193,MATCH($D20,Options!$D$193:$D$193,0)),"")))</f>
+        <f aca="false">IF($E20&lt;&gt;"",$E20,IF($D20="","",IFERROR(INDEX(Options!$F$194:$F$194,MATCH($D20,Options!$D$194:$D$194,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9"/>
       <c r="B21" s="10" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="D21" s="15"/>
       <c r="E21" s="13"/>
@@ -12361,38 +12396,38 @@
     <row r="22" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9"/>
       <c r="B22" s="10" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
       <c r="D22" s="15"/>
       <c r="E22" s="13"/>
       <c r="F22" s="14" t="str">
-        <f aca="false">IF($E22&lt;&gt;"",$E22,IF($D22="","",IFERROR(INDEX(Options!$F$194:$F$197,MATCH($D22,Options!$D$194:$D$197,0)),"")))</f>
+        <f aca="false">IF($E22&lt;&gt;"",$E22,IF($D22="","",IFERROR(INDEX(Options!$F$195:$F$198,MATCH($D22,Options!$D$195:$D$198,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9"/>
       <c r="B23" s="10" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="15"/>
       <c r="E23" s="13"/>
       <c r="F23" s="14" t="str">
-        <f aca="false">IF($E23&lt;&gt;"",$E23,IF($D23="","",IFERROR(INDEX(Options!$F$194:$F$197,MATCH($D23,Options!$D$194:$D$197,0)),"")))</f>
+        <f aca="false">IF($E23&lt;&gt;"",$E23,IF($D23="","",IFERROR(INDEX(Options!$F$195:$F$198,MATCH($D23,Options!$D$195:$D$198,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="24" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9"/>
       <c r="B24" s="10" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
       <c r="D24" s="15"/>
       <c r="E24" s="13"/>
@@ -12403,10 +12438,10 @@
     </row>
     <row r="25" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -12416,10 +12451,10 @@
     <row r="26" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9"/>
       <c r="B26" s="10" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="D26" s="15"/>
       <c r="E26" s="13"/>
@@ -12431,175 +12466,175 @@
     <row r="27" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9"/>
       <c r="B27" s="10" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="D27" s="15"/>
       <c r="E27" s="13"/>
       <c r="F27" s="14" t="str">
-        <f aca="false">IF($E27&lt;&gt;"",$E27,IF($D27="","",IFERROR(INDEX(Options!$F$198:$F$200,MATCH($D27,Options!$D$198:$D$200,0)),"")))</f>
+        <f aca="false">IF($E27&lt;&gt;"",$E27,IF($D27="","",IFERROR(INDEX(Options!$F$199:$F$201,MATCH($D27,Options!$D$199:$D$201,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9"/>
       <c r="B28" s="10" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="15"/>
       <c r="E28" s="13"/>
       <c r="F28" s="14" t="str">
-        <f aca="false">IF($E28&lt;&gt;"",$E28,IF($D28="","",IFERROR(INDEX(Options!$F$198:$F$200,MATCH($D28,Options!$D$198:$D$200,0)),"")))</f>
+        <f aca="false">IF($E28&lt;&gt;"",$E28,IF($D28="","",IFERROR(INDEX(Options!$F$199:$F$201,MATCH($D28,Options!$D$199:$D$201,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="29" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9"/>
       <c r="B29" s="10" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="D29" s="15"/>
       <c r="E29" s="13"/>
       <c r="F29" s="14" t="str">
-        <f aca="false">IF($E29&lt;&gt;"",$E29,IF($D29="","",IFERROR(INDEX(Options!$F$201:$F$205,MATCH($D29,Options!$D$201:$D$205,0)),"")))</f>
+        <f aca="false">IF($E29&lt;&gt;"",$E29,IF($D29="","",IFERROR(INDEX(Options!$F$202:$F$206,MATCH($D29,Options!$D$202:$D$206,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9"/>
       <c r="B30" s="10" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="15"/>
       <c r="E30" s="13"/>
       <c r="F30" s="14" t="str">
-        <f aca="false">IF($E30&lt;&gt;"",$E30,IF($D30="","",IFERROR(INDEX(Options!$F$201:$F$205,MATCH($D30,Options!$D$201:$D$205,0)),"")))</f>
+        <f aca="false">IF($E30&lt;&gt;"",$E30,IF($D30="","",IFERROR(INDEX(Options!$F$202:$F$206,MATCH($D30,Options!$D$202:$D$206,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9"/>
       <c r="B31" s="10" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="15"/>
       <c r="E31" s="13"/>
       <c r="F31" s="14" t="str">
-        <f aca="false">IF($E31&lt;&gt;"",$E31,IF($D31="","",IFERROR(INDEX(Options!$F$201:$F$205,MATCH($D31,Options!$D$201:$D$205,0)),"")))</f>
+        <f aca="false">IF($E31&lt;&gt;"",$E31,IF($D31="","",IFERROR(INDEX(Options!$F$202:$F$206,MATCH($D31,Options!$D$202:$D$206,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="32" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9"/>
       <c r="B32" s="10" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="D32" s="15"/>
       <c r="E32" s="13"/>
       <c r="F32" s="14" t="str">
-        <f aca="false">IF($E32&lt;&gt;"",$E32,IF($D32="","",IFERROR(INDEX(Options!$F$206:$F$211,MATCH($D32,Options!$D$206:$D$211,0)),"")))</f>
+        <f aca="false">IF($E32&lt;&gt;"",$E32,IF($D32="","",IFERROR(INDEX(Options!$F$207:$F$212,MATCH($D32,Options!$D$207:$D$212,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9"/>
       <c r="B33" s="10" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="15"/>
       <c r="E33" s="13"/>
       <c r="F33" s="14" t="str">
-        <f aca="false">IF($E33&lt;&gt;"",$E33,IF($D33="","",IFERROR(INDEX(Options!$F$206:$F$211,MATCH($D33,Options!$D$206:$D$211,0)),"")))</f>
+        <f aca="false">IF($E33&lt;&gt;"",$E33,IF($D33="","",IFERROR(INDEX(Options!$F$207:$F$212,MATCH($D33,Options!$D$207:$D$212,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9"/>
       <c r="B34" s="10" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="15"/>
       <c r="E34" s="13"/>
       <c r="F34" s="14" t="str">
-        <f aca="false">IF($E34&lt;&gt;"",$E34,IF($D34="","",IFERROR(INDEX(Options!$F$206:$F$211,MATCH($D34,Options!$D$206:$D$211,0)),"")))</f>
+        <f aca="false">IF($E34&lt;&gt;"",$E34,IF($D34="","",IFERROR(INDEX(Options!$F$207:$F$212,MATCH($D34,Options!$D$207:$D$212,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="35" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9"/>
       <c r="B35" s="10" t="s">
-        <v>1053</v>
+        <v>1057</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>1054</v>
+        <v>1058</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="13"/>
       <c r="F35" s="14" t="str">
-        <f aca="false">IF($E35&lt;&gt;"",$E35,IF($D35="","",IFERROR(INDEX(Options!$F$212:$F$214,MATCH($D35,Options!$D$212:$D$214,0)),"")))</f>
+        <f aca="false">IF($E35&lt;&gt;"",$E35,IF($D35="","",IFERROR(INDEX(Options!$F$213:$F$215,MATCH($D35,Options!$D$213:$D$215,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9"/>
       <c r="B36" s="10" t="s">
-        <v>1055</v>
+        <v>1059</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="15"/>
       <c r="E36" s="13"/>
       <c r="F36" s="14" t="str">
-        <f aca="false">IF($E36&lt;&gt;"",$E36,IF($D36="","",IFERROR(INDEX(Options!$F$212:$F$214,MATCH($D36,Options!$D$212:$D$214,0)),"")))</f>
+        <f aca="false">IF($E36&lt;&gt;"",$E36,IF($D36="","",IFERROR(INDEX(Options!$F$213:$F$215,MATCH($D36,Options!$D$213:$D$215,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9"/>
       <c r="B37" s="10" t="s">
-        <v>1056</v>
+        <v>1060</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="D37" s="15"/>
       <c r="E37" s="13"/>
       <c r="F37" s="14" t="str">
-        <f aca="false">IF($E37&lt;&gt;"",$E37,IF($D37="","",IFERROR(INDEX(Options!$F$215:$F$217,MATCH($D37,Options!$D$215:$D$217,0)),"")))</f>
+        <f aca="false">IF($E37&lt;&gt;"",$E37,IF($D37="","",IFERROR(INDEX(Options!$F$216:$F$218,MATCH($D37,Options!$D$216:$D$218,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9"/>
       <c r="B38" s="10" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="15"/>
       <c r="E38" s="13"/>
       <c r="F38" s="14" t="str">
-        <f aca="false">IF($E38&lt;&gt;"",$E38,IF($D38="","",IFERROR(INDEX(Options!$F$215:$F$217,MATCH($D38,Options!$D$215:$D$217,0)),"")))</f>
+        <f aca="false">IF($E38&lt;&gt;"",$E38,IF($D38="","",IFERROR(INDEX(Options!$F$216:$F$218,MATCH($D38,Options!$D$216:$D$218,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -12609,10 +12644,10 @@
     <row r="40" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9"/>
       <c r="B40" s="10" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D40" s="15"/>
       <c r="E40" s="13"/>
@@ -12624,52 +12659,52 @@
     <row r="41" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9"/>
       <c r="B41" s="10" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="D41" s="15"/>
       <c r="E41" s="13"/>
       <c r="F41" s="14" t="str">
-        <f aca="false">IF($E41&lt;&gt;"",$E41,IF($D41="","",IFERROR(INDEX(Options!$F$218:$F$220,MATCH($D41,Options!$D$218:$D$220,0)),"")))</f>
+        <f aca="false">IF($E41&lt;&gt;"",$E41,IF($D41="","",IFERROR(INDEX(Options!$F$219:$F$221,MATCH($D41,Options!$D$219:$D$221,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9"/>
       <c r="B42" s="10" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="15"/>
       <c r="E42" s="13"/>
       <c r="F42" s="14" t="str">
-        <f aca="false">IF($E42&lt;&gt;"",$E42,IF($D42="","",IFERROR(INDEX(Options!$F$218:$F$220,MATCH($D42,Options!$D$218:$D$220,0)),"")))</f>
+        <f aca="false">IF($E42&lt;&gt;"",$E42,IF($D42="","",IFERROR(INDEX(Options!$F$219:$F$221,MATCH($D42,Options!$D$219:$D$221,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="43" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9"/>
       <c r="B43" s="10" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="D43" s="15"/>
       <c r="E43" s="13"/>
       <c r="F43" s="14" t="str">
-        <f aca="false">IF($E43&lt;&gt;"",$E43,IF($D43="","",IFERROR(INDEX(Options!$F$221:$F$221,MATCH($D43,Options!$D$221:$D$221,0)),"")))</f>
+        <f aca="false">IF($E43&lt;&gt;"",$E43,IF($D43="","",IFERROR(INDEX(Options!$F$222:$F$222,MATCH($D43,Options!$D$222:$D$222,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -12679,10 +12714,10 @@
     <row r="45" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9"/>
       <c r="B45" s="10" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="D45" s="15"/>
       <c r="E45" s="13"/>
@@ -12694,91 +12729,91 @@
     <row r="46" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9"/>
       <c r="B46" s="10" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="D46" s="15"/>
       <c r="E46" s="13"/>
       <c r="F46" s="14" t="str">
-        <f aca="false">IF($E46&lt;&gt;"",$E46,IF($D46="","",IFERROR(INDEX(Options!$F$222:$F$226,MATCH($D46,Options!$D$222:$D$226,0)),"")))</f>
+        <f aca="false">IF($E46&lt;&gt;"",$E46,IF($D46="","",IFERROR(INDEX(Options!$F$223:$F$227,MATCH($D46,Options!$D$223:$D$227,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9"/>
       <c r="B47" s="10" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="15"/>
       <c r="E47" s="13"/>
       <c r="F47" s="14" t="str">
-        <f aca="false">IF($E47&lt;&gt;"",$E47,IF($D47="","",IFERROR(INDEX(Options!$F$222:$F$226,MATCH($D47,Options!$D$222:$D$226,0)),"")))</f>
+        <f aca="false">IF($E47&lt;&gt;"",$E47,IF($D47="","",IFERROR(INDEX(Options!$F$223:$F$227,MATCH($D47,Options!$D$223:$D$227,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9"/>
       <c r="B48" s="10" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="15"/>
       <c r="E48" s="13"/>
       <c r="F48" s="14" t="str">
-        <f aca="false">IF($E48&lt;&gt;"",$E48,IF($D48="","",IFERROR(INDEX(Options!$F$222:$F$226,MATCH($D48,Options!$D$222:$D$226,0)),"")))</f>
+        <f aca="false">IF($E48&lt;&gt;"",$E48,IF($D48="","",IFERROR(INDEX(Options!$F$223:$F$227,MATCH($D48,Options!$D$223:$D$227,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="49" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9"/>
       <c r="B49" s="10" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="D49" s="15"/>
       <c r="E49" s="13"/>
       <c r="F49" s="14" t="str">
-        <f aca="false">IF($E49&lt;&gt;"",$E49,IF($D49="","",IFERROR(INDEX(Options!$F$227:$F$230,MATCH($D49,Options!$D$227:$D$230,0)),"")))</f>
+        <f aca="false">IF($E49&lt;&gt;"",$E49,IF($D49="","",IFERROR(INDEX(Options!$F$228:$F$231,MATCH($D49,Options!$D$228:$D$231,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9"/>
       <c r="B50" s="10" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="15"/>
       <c r="E50" s="13"/>
       <c r="F50" s="14" t="str">
-        <f aca="false">IF($E50&lt;&gt;"",$E50,IF($D50="","",IFERROR(INDEX(Options!$F$227:$F$230,MATCH($D50,Options!$D$227:$D$230,0)),"")))</f>
+        <f aca="false">IF($E50&lt;&gt;"",$E50,IF($D50="","",IFERROR(INDEX(Options!$F$228:$F$231,MATCH($D50,Options!$D$228:$D$231,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9"/>
       <c r="B51" s="10" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="15"/>
       <c r="E51" s="13"/>
       <c r="F51" s="14" t="str">
-        <f aca="false">IF($E51&lt;&gt;"",$E51,IF($D51="","",IFERROR(INDEX(Options!$F$227:$F$230,MATCH($D51,Options!$D$227:$D$230,0)),"")))</f>
+        <f aca="false">IF($E51&lt;&gt;"",$E51,IF($D51="","",IFERROR(INDEX(Options!$F$228:$F$231,MATCH($D51,Options!$D$228:$D$231,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="52" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="C52" s="8"/>
       <c r="D52" s="8"/>
@@ -12788,10 +12823,10 @@
     <row r="53" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9"/>
       <c r="B53" s="10" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="D53" s="15"/>
       <c r="E53" s="13"/>
@@ -12803,104 +12838,104 @@
     <row r="54" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9"/>
       <c r="B54" s="10" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="D54" s="15"/>
       <c r="E54" s="13"/>
       <c r="F54" s="14" t="str">
-        <f aca="false">IF($E54&lt;&gt;"",$E54,IF($D54="","",IFERROR(INDEX(Options!$F$231:$F$240,MATCH($D54,Options!$D$231:$D$240,0)),"")))</f>
+        <f aca="false">IF($E54&lt;&gt;"",$E54,IF($D54="","",IFERROR(INDEX(Options!$F$232:$F$241,MATCH($D54,Options!$D$232:$D$241,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9"/>
       <c r="B55" s="10" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="15"/>
       <c r="E55" s="13"/>
       <c r="F55" s="14" t="str">
-        <f aca="false">IF($E55&lt;&gt;"",$E55,IF($D55="","",IFERROR(INDEX(Options!$F$231:$F$240,MATCH($D55,Options!$D$231:$D$240,0)),"")))</f>
+        <f aca="false">IF($E55&lt;&gt;"",$E55,IF($D55="","",IFERROR(INDEX(Options!$F$232:$F$241,MATCH($D55,Options!$D$232:$D$241,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9"/>
       <c r="B56" s="10" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="15"/>
       <c r="E56" s="13"/>
       <c r="F56" s="14" t="str">
-        <f aca="false">IF($E56&lt;&gt;"",$E56,IF($D56="","",IFERROR(INDEX(Options!$F$231:$F$240,MATCH($D56,Options!$D$231:$D$240,0)),"")))</f>
+        <f aca="false">IF($E56&lt;&gt;"",$E56,IF($D56="","",IFERROR(INDEX(Options!$F$232:$F$241,MATCH($D56,Options!$D$232:$D$241,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9"/>
       <c r="B57" s="10" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="15"/>
       <c r="E57" s="13"/>
       <c r="F57" s="14" t="str">
-        <f aca="false">IF($E57&lt;&gt;"",$E57,IF($D57="","",IFERROR(INDEX(Options!$F$231:$F$240,MATCH($D57,Options!$D$231:$D$240,0)),"")))</f>
+        <f aca="false">IF($E57&lt;&gt;"",$E57,IF($D57="","",IFERROR(INDEX(Options!$F$232:$F$241,MATCH($D57,Options!$D$232:$D$241,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="58" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9"/>
       <c r="B58" s="10" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="D58" s="15"/>
       <c r="E58" s="13"/>
       <c r="F58" s="14" t="str">
-        <f aca="false">IF($E58&lt;&gt;"",$E58,IF($D58="","",IFERROR(INDEX(Options!$F$241:$F$244,MATCH($D58,Options!$D$241:$D$244,0)),"")))</f>
+        <f aca="false">IF($E58&lt;&gt;"",$E58,IF($D58="","",IFERROR(INDEX(Options!$F$242:$F$245,MATCH($D58,Options!$D$242:$D$245,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9"/>
       <c r="B59" s="10" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="15"/>
       <c r="E59" s="13"/>
       <c r="F59" s="14" t="str">
-        <f aca="false">IF($E59&lt;&gt;"",$E59,IF($D59="","",IFERROR(INDEX(Options!$F$241:$F$244,MATCH($D59,Options!$D$241:$D$244,0)),"")))</f>
+        <f aca="false">IF($E59&lt;&gt;"",$E59,IF($D59="","",IFERROR(INDEX(Options!$F$242:$F$245,MATCH($D59,Options!$D$242:$D$245,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9"/>
       <c r="B60" s="10" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
       <c r="C60" s="9"/>
       <c r="D60" s="15"/>
       <c r="E60" s="13"/>
       <c r="F60" s="14" t="str">
-        <f aca="false">IF($E60&lt;&gt;"",$E60,IF($D60="","",IFERROR(INDEX(Options!$F$241:$F$244,MATCH($D60,Options!$D$241:$D$244,0)),"")))</f>
+        <f aca="false">IF($E60&lt;&gt;"",$E60,IF($D60="","",IFERROR(INDEX(Options!$F$242:$F$245,MATCH($D60,Options!$D$242:$D$245,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="61" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -12910,10 +12945,10 @@
     <row r="62" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9"/>
       <c r="B62" s="10" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="D62" s="15"/>
       <c r="E62" s="13"/>
@@ -12925,65 +12960,65 @@
     <row r="63" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9"/>
       <c r="B63" s="10" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="D63" s="15"/>
       <c r="E63" s="13"/>
       <c r="F63" s="14" t="str">
-        <f aca="false">IF($E63&lt;&gt;"",$E63,IF($D63="","",IFERROR(INDEX(Options!$F$245:$F$247,MATCH($D63,Options!$D$245:$D$247,0)),"")))</f>
+        <f aca="false">IF($E63&lt;&gt;"",$E63,IF($D63="","",IFERROR(INDEX(Options!$F$246:$F$248,MATCH($D63,Options!$D$246:$D$248,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9"/>
       <c r="B64" s="10" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="15"/>
       <c r="E64" s="13"/>
       <c r="F64" s="14" t="str">
-        <f aca="false">IF($E64&lt;&gt;"",$E64,IF($D64="","",IFERROR(INDEX(Options!$F$245:$F$247,MATCH($D64,Options!$D$245:$D$247,0)),"")))</f>
+        <f aca="false">IF($E64&lt;&gt;"",$E64,IF($D64="","",IFERROR(INDEX(Options!$F$246:$F$248,MATCH($D64,Options!$D$246:$D$248,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="65" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9"/>
       <c r="B65" s="10" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="D65" s="15"/>
       <c r="E65" s="13"/>
       <c r="F65" s="14" t="str">
-        <f aca="false">IF($E65&lt;&gt;"",$E65,IF($D65="","",IFERROR(INDEX(Options!$F$248:$F$250,MATCH($D65,Options!$D$248:$D$250,0)),"")))</f>
+        <f aca="false">IF($E65&lt;&gt;"",$E65,IF($D65="","",IFERROR(INDEX(Options!$F$249:$F$251,MATCH($D65,Options!$D$249:$D$251,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9"/>
       <c r="B66" s="10" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="15"/>
       <c r="E66" s="13"/>
       <c r="F66" s="14" t="str">
-        <f aca="false">IF($E66&lt;&gt;"",$E66,IF($D66="","",IFERROR(INDEX(Options!$F$248:$F$250,MATCH($D66,Options!$D$248:$D$250,0)),"")))</f>
+        <f aca="false">IF($E66&lt;&gt;"",$E66,IF($D66="","",IFERROR(INDEX(Options!$F$249:$F$251,MATCH($D66,Options!$D$249:$D$251,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="C67" s="8"/>
       <c r="D67" s="8"/>
@@ -12993,10 +13028,10 @@
     <row r="68" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9"/>
       <c r="B68" s="10" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="D68" s="15"/>
       <c r="E68" s="13"/>
@@ -13008,119 +13043,119 @@
     <row r="69" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9"/>
       <c r="B69" s="10" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="D69" s="15"/>
       <c r="E69" s="13"/>
       <c r="F69" s="14" t="str">
-        <f aca="false">IF($E69&lt;&gt;"",$E69,IF($D69="","",IFERROR(INDEX(Options!$F$251:$F$255,MATCH($D69,Options!$D$251:$D$255,0)),"")))</f>
+        <f aca="false">IF($E69&lt;&gt;"",$E69,IF($D69="","",IFERROR(INDEX(Options!$F$252:$F$256,MATCH($D69,Options!$D$252:$D$256,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9"/>
       <c r="B70" s="10" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="15"/>
       <c r="E70" s="13"/>
       <c r="F70" s="14" t="str">
-        <f aca="false">IF($E70&lt;&gt;"",$E70,IF($D70="","",IFERROR(INDEX(Options!$F$251:$F$255,MATCH($D70,Options!$D$251:$D$255,0)),"")))</f>
+        <f aca="false">IF($E70&lt;&gt;"",$E70,IF($D70="","",IFERROR(INDEX(Options!$F$252:$F$256,MATCH($D70,Options!$D$252:$D$256,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="9"/>
       <c r="B71" s="10" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="15"/>
       <c r="E71" s="13"/>
       <c r="F71" s="14" t="str">
-        <f aca="false">IF($E71&lt;&gt;"",$E71,IF($D71="","",IFERROR(INDEX(Options!$F$251:$F$255,MATCH($D71,Options!$D$251:$D$255,0)),"")))</f>
+        <f aca="false">IF($E71&lt;&gt;"",$E71,IF($D71="","",IFERROR(INDEX(Options!$F$252:$F$256,MATCH($D71,Options!$D$252:$D$256,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="72" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9"/>
       <c r="B72" s="10" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="D72" s="15"/>
       <c r="E72" s="13"/>
       <c r="F72" s="14" t="str">
-        <f aca="false">IF($E72&lt;&gt;"",$E72,IF($D72="","",IFERROR(INDEX(Options!$F$256:$F$262,MATCH($D72,Options!$D$256:$D$262,0)),"")))</f>
+        <f aca="false">IF($E72&lt;&gt;"",$E72,IF($D72="","",IFERROR(INDEX(Options!$F$257:$F$263,MATCH($D72,Options!$D$257:$D$263,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9"/>
       <c r="B73" s="10" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="15"/>
       <c r="E73" s="13"/>
       <c r="F73" s="14" t="str">
-        <f aca="false">IF($E73&lt;&gt;"",$E73,IF($D73="","",IFERROR(INDEX(Options!$F$256:$F$262,MATCH($D73,Options!$D$256:$D$262,0)),"")))</f>
+        <f aca="false">IF($E73&lt;&gt;"",$E73,IF($D73="","",IFERROR(INDEX(Options!$F$257:$F$263,MATCH($D73,Options!$D$257:$D$263,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="9"/>
       <c r="B74" s="10" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="15"/>
       <c r="E74" s="13"/>
       <c r="F74" s="14" t="str">
-        <f aca="false">IF($E74&lt;&gt;"",$E74,IF($D74="","",IFERROR(INDEX(Options!$F$256:$F$262,MATCH($D74,Options!$D$256:$D$262,0)),"")))</f>
+        <f aca="false">IF($E74&lt;&gt;"",$E74,IF($D74="","",IFERROR(INDEX(Options!$F$257:$F$263,MATCH($D74,Options!$D$257:$D$263,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9"/>
       <c r="B75" s="10" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="15"/>
       <c r="E75" s="13"/>
       <c r="F75" s="14" t="str">
-        <f aca="false">IF($E75&lt;&gt;"",$E75,IF($D75="","",IFERROR(INDEX(Options!$F$256:$F$262,MATCH($D75,Options!$D$256:$D$262,0)),"")))</f>
+        <f aca="false">IF($E75&lt;&gt;"",$E75,IF($D75="","",IFERROR(INDEX(Options!$F$257:$F$263,MATCH($D75,Options!$D$257:$D$263,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="76" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="9"/>
       <c r="B76" s="10" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="D76" s="15"/>
       <c r="E76" s="13"/>
       <c r="F76" s="14" t="str">
-        <f aca="false">IF($E76&lt;&gt;"",$E76,IF($D76="","",IFERROR(INDEX(Options!$F$263:$F$267,MATCH($D76,Options!$D$263:$D$267,0)),"")))</f>
+        <f aca="false">IF($E76&lt;&gt;"",$E76,IF($D76="","",IFERROR(INDEX(Options!$F$264:$F$268,MATCH($D76,Options!$D$264:$D$268,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="77" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B77" s="7" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
@@ -13130,63 +13165,63 @@
     <row r="78" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="9"/>
       <c r="B78" s="10" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="D78" s="15"/>
       <c r="E78" s="13"/>
       <c r="F78" s="14" t="str">
-        <f aca="false">IF($E78&lt;&gt;"",$E78,IF($D78="","",IFERROR(INDEX(Options!$F$268:$F$273,MATCH($D78,Options!$D$268:$D$273,0)),"")))</f>
+        <f aca="false">IF($E78&lt;&gt;"",$E78,IF($D78="","",IFERROR(INDEX(Options!$F$269:$F$274,MATCH($D78,Options!$D$269:$D$274,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="9"/>
       <c r="B79" s="10" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="15"/>
       <c r="E79" s="13"/>
       <c r="F79" s="14" t="str">
-        <f aca="false">IF($E79&lt;&gt;"",$E79,IF($D79="","",IFERROR(INDEX(Options!$F$268:$F$273,MATCH($D79,Options!$D$268:$D$273,0)),"")))</f>
+        <f aca="false">IF($E79&lt;&gt;"",$E79,IF($D79="","",IFERROR(INDEX(Options!$F$269:$F$274,MATCH($D79,Options!$D$269:$D$274,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="9"/>
       <c r="B80" s="10" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="15"/>
       <c r="E80" s="13"/>
       <c r="F80" s="14" t="str">
-        <f aca="false">IF($E80&lt;&gt;"",$E80,IF($D80="","",IFERROR(INDEX(Options!$F$268:$F$273,MATCH($D80,Options!$D$268:$D$273,0)),"")))</f>
+        <f aca="false">IF($E80&lt;&gt;"",$E80,IF($D80="","",IFERROR(INDEX(Options!$F$269:$F$274,MATCH($D80,Options!$D$269:$D$274,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="9"/>
       <c r="B81" s="10" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="15"/>
       <c r="E81" s="13"/>
       <c r="F81" s="14" t="str">
-        <f aca="false">IF($E81&lt;&gt;"",$E81,IF($D81="","",IFERROR(INDEX(Options!$F$268:$F$273,MATCH($D81,Options!$D$268:$D$273,0)),"")))</f>
+        <f aca="false">IF($E81&lt;&gt;"",$E81,IF($D81="","",IFERROR(INDEX(Options!$F$269:$F$274,MATCH($D81,Options!$D$269:$D$274,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="82" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="B82" s="7" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="C82" s="8"/>
       <c r="D82" s="8"/>
@@ -13196,50 +13231,50 @@
     <row r="83" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="9"/>
       <c r="B83" s="10" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="D83" s="15"/>
       <c r="E83" s="13"/>
       <c r="F83" s="14" t="str">
-        <f aca="false">IF($E83&lt;&gt;"",$E83,IF($D83="","",IFERROR(INDEX(Options!$F$274:$F$279,MATCH($D83,Options!$D$274:$D$279,0)),"")))</f>
+        <f aca="false">IF($E83&lt;&gt;"",$E83,IF($D83="","",IFERROR(INDEX(Options!$F$275:$F$280,MATCH($D83,Options!$D$275:$D$280,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9"/>
       <c r="B84" s="10" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="C84" s="9"/>
       <c r="D84" s="15"/>
       <c r="E84" s="13"/>
       <c r="F84" s="14" t="str">
-        <f aca="false">IF($E84&lt;&gt;"",$E84,IF($D84="","",IFERROR(INDEX(Options!$F$274:$F$279,MATCH($D84,Options!$D$274:$D$279,0)),"")))</f>
+        <f aca="false">IF($E84&lt;&gt;"",$E84,IF($D84="","",IFERROR(INDEX(Options!$F$275:$F$280,MATCH($D84,Options!$D$275:$D$280,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9"/>
       <c r="B85" s="10" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="15"/>
       <c r="E85" s="13"/>
       <c r="F85" s="14" t="str">
-        <f aca="false">IF($E85&lt;&gt;"",$E85,IF($D85="","",IFERROR(INDEX(Options!$F$274:$F$279,MATCH($D85,Options!$D$274:$D$279,0)),"")))</f>
+        <f aca="false">IF($E85&lt;&gt;"",$E85,IF($D85="","",IFERROR(INDEX(Options!$F$275:$F$280,MATCH($D85,Options!$D$275:$D$280,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="86" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B86" s="7" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="C86" s="8"/>
       <c r="D86" s="8"/>
@@ -13249,82 +13284,82 @@
     <row r="87" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="9"/>
       <c r="B87" s="10" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="D87" s="15"/>
       <c r="E87" s="13"/>
       <c r="F87" s="14" t="str">
-        <f aca="false">IF($E87&lt;&gt;"",$E87,IF($D87="","",IFERROR(INDEX(Options!$F$280:$F$285,MATCH($D87,Options!$D$280:$D$285,0)),"")))</f>
+        <f aca="false">IF($E87&lt;&gt;"",$E87,IF($D87="","",IFERROR(INDEX(Options!$F$281:$F$286,MATCH($D87,Options!$D$281:$D$286,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="9"/>
       <c r="B88" s="10" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="C88" s="9"/>
       <c r="D88" s="15"/>
       <c r="E88" s="13"/>
       <c r="F88" s="14" t="str">
-        <f aca="false">IF($E88&lt;&gt;"",$E88,IF($D88="","",IFERROR(INDEX(Options!$F$280:$F$285,MATCH($D88,Options!$D$280:$D$285,0)),"")))</f>
+        <f aca="false">IF($E88&lt;&gt;"",$E88,IF($D88="","",IFERROR(INDEX(Options!$F$281:$F$286,MATCH($D88,Options!$D$281:$D$286,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="9"/>
       <c r="B89" s="10" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="15"/>
       <c r="E89" s="13"/>
       <c r="F89" s="14" t="str">
-        <f aca="false">IF($E89&lt;&gt;"",$E89,IF($D89="","",IFERROR(INDEX(Options!$F$280:$F$285,MATCH($D89,Options!$D$280:$D$285,0)),"")))</f>
+        <f aca="false">IF($E89&lt;&gt;"",$E89,IF($D89="","",IFERROR(INDEX(Options!$F$281:$F$286,MATCH($D89,Options!$D$281:$D$286,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="9"/>
       <c r="B90" s="10" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="C90" s="9"/>
       <c r="D90" s="15"/>
       <c r="E90" s="13"/>
       <c r="F90" s="14" t="str">
-        <f aca="false">IF($E90&lt;&gt;"",$E90,IF($D90="","",IFERROR(INDEX(Options!$F$280:$F$285,MATCH($D90,Options!$D$280:$D$285,0)),"")))</f>
+        <f aca="false">IF($E90&lt;&gt;"",$E90,IF($D90="","",IFERROR(INDEX(Options!$F$281:$F$286,MATCH($D90,Options!$D$281:$D$286,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="91" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="9"/>
       <c r="B91" s="10" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="D91" s="15"/>
       <c r="E91" s="13"/>
       <c r="F91" s="14" t="str">
-        <f aca="false">IF($E91&lt;&gt;"",$E91,IF($D91="","",IFERROR(INDEX(Options!$F$286:$F$287,MATCH($D91,Options!$D$286:$D$287,0)),"")))</f>
+        <f aca="false">IF($E91&lt;&gt;"",$E91,IF($D91="","",IFERROR(INDEX(Options!$F$287:$F$288,MATCH($D91,Options!$D$287:$D$288,0)),"")))</f>
         <v/>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9"/>
       <c r="B92" s="10" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="C92" s="9"/>
       <c r="D92" s="15"/>
       <c r="E92" s="13"/>
       <c r="F92" s="14" t="str">
-        <f aca="false">IF($E92&lt;&gt;"",$E92,IF($D92="","",IFERROR(INDEX(Options!$F$286:$F$287,MATCH($D92,Options!$D$286:$D$287,0)),"")))</f>
+        <f aca="false">IF($E92&lt;&gt;"",$E92,IF($D92="","",IFERROR(INDEX(Options!$F$287:$F$288,MATCH($D92,Options!$D$287:$D$288,0)),"")))</f>
         <v/>
       </c>
     </row>
@@ -13459,12 +13494,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="619.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13551,12 +13586,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="619.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13669,13 +13704,13 @@
         <v>15</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13686,13 +13721,13 @@
         <v>22</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13703,13 +13738,13 @@
         <v>144</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13720,13 +13755,13 @@
         <v>262</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13737,13 +13772,13 @@
         <v>315</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13754,16 +13789,16 @@
         <v>506</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>1148</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
@@ -13771,13 +13806,13 @@
         <v>533</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13785,220 +13820,220 @@
         <v>21</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>262</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
     </row>
   </sheetData>
